--- a/product-definitions/spreadsheet/aerosol-size-distribution.xlsx
+++ b/product-definitions/spreadsheet/aerosol-size-distribution.xlsx
@@ -373,7 +373,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -396,9 +396,6 @@
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
@@ -448,9 +445,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
@@ -836,7 +830,7 @@
       <c r="A5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -872,7 +866,7 @@
       <c r="A6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -7712,28 +7706,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.0" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" ht="12.0" customHeight="1">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -7742,621 +7736,621 @@
       <c r="C2" s="5">
         <v>1.0</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
     </row>
     <row r="3" ht="12.0" customHeight="1">
-      <c r="A3" s="10"/>
+      <c r="A3" s="9"/>
       <c r="B3" s="5"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" ht="12.0" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="13"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="12"/>
     </row>
     <row r="5" ht="12.0" customHeight="1">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
     </row>
     <row r="6" ht="12.0" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
     </row>
     <row r="7" ht="12.0" customHeight="1">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
     </row>
     <row r="8" ht="12.0" customHeight="1">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
     </row>
     <row r="9" ht="12.0" customHeight="1">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
     </row>
     <row r="10" ht="12.0" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
     </row>
     <row r="11" ht="12.0" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
     </row>
     <row r="12" ht="12.0" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
     </row>
     <row r="13" ht="12.0" customHeight="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
     </row>
     <row r="14" ht="12.0" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
     </row>
     <row r="15" ht="12.0" customHeight="1">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
     </row>
     <row r="16" ht="12.0" customHeight="1">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" ht="12.0" customHeight="1">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
     </row>
     <row r="18" ht="12.0" customHeight="1">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
     </row>
     <row r="19" ht="12.0" customHeight="1">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" ht="12.0" customHeight="1">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
     </row>
     <row r="21" ht="12.0" customHeight="1">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" ht="12.0" customHeight="1">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" ht="12.0" customHeight="1">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" ht="12.0" customHeight="1">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
     </row>
     <row r="25" ht="12.0" customHeight="1">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
     </row>
     <row r="26" ht="12.0" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
     </row>
     <row r="27" ht="12.0" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
     </row>
     <row r="28" ht="12.0" customHeight="1">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
     </row>
     <row r="29" ht="12.0" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
     </row>
     <row r="30" ht="12.0" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
     </row>
     <row r="31" ht="12.0" customHeight="1">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
     </row>
     <row r="32" ht="12.0" customHeight="1">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
     </row>
     <row r="33" ht="12.0" customHeight="1">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
     </row>
     <row r="34" ht="12.0" customHeight="1">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
     </row>
     <row r="35" ht="12.0" customHeight="1">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
     </row>
     <row r="36" ht="12.0" customHeight="1">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
     </row>
     <row r="37" ht="12.0" customHeight="1">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
     </row>
     <row r="38" ht="12.0" customHeight="1">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
     </row>
     <row r="39" ht="12.0" customHeight="1">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
     </row>
     <row r="40" ht="12.0" customHeight="1">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
     </row>
     <row r="41" ht="12.0" customHeight="1">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
     </row>
     <row r="42" ht="12.0" customHeight="1">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
+      <c r="A42" s="9"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
     </row>
     <row r="43" ht="12.0" customHeight="1">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
     </row>
     <row r="44" ht="12.0" customHeight="1">
-      <c r="A44" s="10"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
     </row>
     <row r="45" ht="12.0" customHeight="1">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
     </row>
     <row r="46" ht="12.0" customHeight="1">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
+      <c r="A46" s="9"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
     </row>
     <row r="47" ht="12.0" customHeight="1">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
+      <c r="A47" s="9"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
     </row>
     <row r="48" ht="12.0" customHeight="1">
-      <c r="A48" s="10"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
     </row>
     <row r="49" ht="12.0" customHeight="1">
-      <c r="A49" s="10"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
     </row>
     <row r="50" ht="12.0" customHeight="1">
-      <c r="A50" s="10"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
+      <c r="A50" s="9"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
     </row>
     <row r="51" ht="12.0" customHeight="1">
-      <c r="A51" s="10"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
+      <c r="A51" s="9"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
     </row>
     <row r="52" ht="12.0" customHeight="1">
-      <c r="A52" s="10"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
+      <c r="A52" s="9"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
     </row>
     <row r="53" ht="12.0" customHeight="1">
-      <c r="A53" s="10"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
+      <c r="A53" s="9"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
     </row>
     <row r="54" ht="12.0" customHeight="1">
-      <c r="A54" s="10"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
+      <c r="A54" s="9"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
     </row>
     <row r="55" ht="12.0" customHeight="1">
-      <c r="A55" s="10"/>
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
+      <c r="A55" s="9"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
     </row>
     <row r="56" ht="12.0" customHeight="1">
-      <c r="A56" s="10"/>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
+      <c r="A56" s="9"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
     </row>
     <row r="57" ht="12.0" customHeight="1">
-      <c r="A57" s="10"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
+      <c r="A57" s="9"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
     </row>
     <row r="58" ht="12.0" customHeight="1">
-      <c r="A58" s="10"/>
-      <c r="B58" s="10"/>
-      <c r="C58" s="10"/>
+      <c r="A58" s="9"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
     </row>
     <row r="59" ht="12.0" customHeight="1">
-      <c r="A59" s="10"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
+      <c r="A59" s="9"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
     </row>
     <row r="60" ht="12.0" customHeight="1">
-      <c r="A60" s="10"/>
-      <c r="B60" s="10"/>
-      <c r="C60" s="10"/>
+      <c r="A60" s="9"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
     </row>
     <row r="61" ht="12.0" customHeight="1">
-      <c r="A61" s="10"/>
-      <c r="B61" s="10"/>
-      <c r="C61" s="10"/>
+      <c r="A61" s="9"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
     </row>
     <row r="62" ht="12.0" customHeight="1">
-      <c r="A62" s="10"/>
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
+      <c r="A62" s="9"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
     </row>
     <row r="63" ht="12.0" customHeight="1">
-      <c r="A63" s="10"/>
-      <c r="B63" s="10"/>
-      <c r="C63" s="10"/>
+      <c r="A63" s="9"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
     </row>
     <row r="64" ht="12.0" customHeight="1">
-      <c r="A64" s="10"/>
-      <c r="B64" s="10"/>
-      <c r="C64" s="10"/>
+      <c r="A64" s="9"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
     </row>
     <row r="65" ht="12.0" customHeight="1">
-      <c r="A65" s="10"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
+      <c r="A65" s="9"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
     </row>
     <row r="66" ht="12.0" customHeight="1">
-      <c r="A66" s="10"/>
-      <c r="B66" s="10"/>
-      <c r="C66" s="10"/>
+      <c r="A66" s="9"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
     </row>
     <row r="67" ht="12.0" customHeight="1">
-      <c r="A67" s="10"/>
-      <c r="B67" s="10"/>
-      <c r="C67" s="10"/>
+      <c r="A67" s="9"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
     </row>
     <row r="68" ht="12.0" customHeight="1">
-      <c r="A68" s="10"/>
-      <c r="B68" s="10"/>
-      <c r="C68" s="10"/>
+      <c r="A68" s="9"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
     </row>
     <row r="69" ht="12.0" customHeight="1">
-      <c r="A69" s="10"/>
-      <c r="B69" s="10"/>
-      <c r="C69" s="10"/>
+      <c r="A69" s="9"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
     </row>
     <row r="70" ht="12.0" customHeight="1">
-      <c r="A70" s="10"/>
-      <c r="B70" s="10"/>
-      <c r="C70" s="10"/>
+      <c r="A70" s="9"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
     </row>
     <row r="71" ht="12.0" customHeight="1">
-      <c r="A71" s="10"/>
-      <c r="B71" s="10"/>
-      <c r="C71" s="10"/>
+      <c r="A71" s="9"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
     </row>
     <row r="72" ht="12.0" customHeight="1">
-      <c r="A72" s="10"/>
-      <c r="B72" s="10"/>
-      <c r="C72" s="10"/>
+      <c r="A72" s="9"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
     </row>
     <row r="73" ht="12.0" customHeight="1">
-      <c r="A73" s="10"/>
-      <c r="B73" s="10"/>
-      <c r="C73" s="10"/>
+      <c r="A73" s="9"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
     </row>
     <row r="74" ht="12.0" customHeight="1">
-      <c r="A74" s="10"/>
-      <c r="B74" s="10"/>
-      <c r="C74" s="10"/>
+      <c r="A74" s="9"/>
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
     </row>
     <row r="75" ht="12.0" customHeight="1">
-      <c r="A75" s="10"/>
-      <c r="B75" s="10"/>
-      <c r="C75" s="10"/>
+      <c r="A75" s="9"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
     </row>
     <row r="76" ht="12.0" customHeight="1">
-      <c r="A76" s="10"/>
-      <c r="B76" s="10"/>
-      <c r="C76" s="10"/>
+      <c r="A76" s="9"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
     </row>
     <row r="77" ht="12.0" customHeight="1">
-      <c r="A77" s="10"/>
-      <c r="B77" s="10"/>
-      <c r="C77" s="10"/>
+      <c r="A77" s="9"/>
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
     </row>
     <row r="78" ht="12.0" customHeight="1">
-      <c r="A78" s="10"/>
-      <c r="B78" s="10"/>
-      <c r="C78" s="10"/>
+      <c r="A78" s="9"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
     </row>
     <row r="79" ht="12.0" customHeight="1">
-      <c r="A79" s="10"/>
-      <c r="B79" s="10"/>
-      <c r="C79" s="10"/>
+      <c r="A79" s="9"/>
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
     </row>
     <row r="80" ht="12.0" customHeight="1">
-      <c r="A80" s="10"/>
-      <c r="B80" s="10"/>
-      <c r="C80" s="10"/>
+      <c r="A80" s="9"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
     </row>
     <row r="81" ht="12.0" customHeight="1">
-      <c r="A81" s="10"/>
-      <c r="B81" s="10"/>
-      <c r="C81" s="10"/>
+      <c r="A81" s="9"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
     </row>
     <row r="82" ht="12.0" customHeight="1">
-      <c r="A82" s="10"/>
-      <c r="B82" s="10"/>
-      <c r="C82" s="10"/>
+      <c r="A82" s="9"/>
+      <c r="B82" s="9"/>
+      <c r="C82" s="9"/>
     </row>
     <row r="83" ht="12.0" customHeight="1">
-      <c r="A83" s="10"/>
-      <c r="B83" s="10"/>
-      <c r="C83" s="10"/>
+      <c r="A83" s="9"/>
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
     </row>
     <row r="84" ht="12.0" customHeight="1">
-      <c r="A84" s="10"/>
-      <c r="B84" s="10"/>
-      <c r="C84" s="10"/>
+      <c r="A84" s="9"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="9"/>
     </row>
     <row r="85" ht="12.0" customHeight="1">
-      <c r="A85" s="10"/>
-      <c r="B85" s="10"/>
-      <c r="C85" s="10"/>
+      <c r="A85" s="9"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="9"/>
     </row>
     <row r="86" ht="12.0" customHeight="1">
-      <c r="A86" s="10"/>
-      <c r="B86" s="10"/>
-      <c r="C86" s="10"/>
+      <c r="A86" s="9"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="9"/>
     </row>
     <row r="87" ht="12.0" customHeight="1">
-      <c r="A87" s="10"/>
-      <c r="B87" s="10"/>
-      <c r="C87" s="10"/>
+      <c r="A87" s="9"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="9"/>
     </row>
     <row r="88" ht="12.0" customHeight="1">
-      <c r="A88" s="10"/>
-      <c r="B88" s="10"/>
-      <c r="C88" s="10"/>
+      <c r="A88" s="9"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="9"/>
     </row>
     <row r="89" ht="12.0" customHeight="1">
-      <c r="A89" s="10"/>
-      <c r="B89" s="10"/>
-      <c r="C89" s="10"/>
+      <c r="A89" s="9"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="9"/>
     </row>
     <row r="90" ht="12.0" customHeight="1">
-      <c r="A90" s="10"/>
-      <c r="B90" s="10"/>
-      <c r="C90" s="10"/>
+      <c r="A90" s="9"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
     </row>
     <row r="91" ht="12.0" customHeight="1">
-      <c r="A91" s="10"/>
-      <c r="B91" s="10"/>
-      <c r="C91" s="10"/>
+      <c r="A91" s="9"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="9"/>
     </row>
     <row r="92" ht="12.0" customHeight="1">
-      <c r="A92" s="10"/>
-      <c r="B92" s="10"/>
-      <c r="C92" s="10"/>
+      <c r="A92" s="9"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="9"/>
     </row>
     <row r="93" ht="12.0" customHeight="1">
-      <c r="A93" s="10"/>
-      <c r="B93" s="10"/>
-      <c r="C93" s="10"/>
+      <c r="A93" s="9"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="9"/>
     </row>
     <row r="94" ht="12.0" customHeight="1">
-      <c r="A94" s="10"/>
-      <c r="B94" s="10"/>
-      <c r="C94" s="10"/>
+      <c r="A94" s="9"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="9"/>
     </row>
     <row r="95" ht="12.0" customHeight="1">
-      <c r="A95" s="10"/>
-      <c r="B95" s="10"/>
-      <c r="C95" s="10"/>
+      <c r="A95" s="9"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
     </row>
     <row r="96" ht="12.0" customHeight="1">
-      <c r="A96" s="10"/>
-      <c r="B96" s="10"/>
-      <c r="C96" s="10"/>
+      <c r="A96" s="9"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="9"/>
     </row>
     <row r="97" ht="12.0" customHeight="1">
-      <c r="A97" s="10"/>
-      <c r="B97" s="10"/>
-      <c r="C97" s="10"/>
+      <c r="A97" s="9"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="9"/>
     </row>
     <row r="98" ht="12.0" customHeight="1">
-      <c r="A98" s="10"/>
-      <c r="B98" s="10"/>
-      <c r="C98" s="10"/>
+      <c r="A98" s="9"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
     </row>
     <row r="99" ht="12.0" customHeight="1">
-      <c r="A99" s="10"/>
-      <c r="B99" s="10"/>
-      <c r="C99" s="10"/>
+      <c r="A99" s="9"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9"/>
     </row>
     <row r="100" ht="12.0" customHeight="1">
-      <c r="A100" s="10"/>
-      <c r="B100" s="10"/>
-      <c r="C100" s="10"/>
+      <c r="A100" s="9"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9"/>
     </row>
     <row r="101" ht="12.0" customHeight="1">
-      <c r="A101" s="10"/>
-      <c r="B101" s="10"/>
-      <c r="C101" s="10"/>
+      <c r="A101" s="9"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
     </row>
     <row r="102" ht="12.0" customHeight="1">
-      <c r="A102" s="10"/>
-      <c r="B102" s="10"/>
-      <c r="C102" s="10"/>
+      <c r="A102" s="9"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="9"/>
     </row>
     <row r="103" ht="12.0" customHeight="1">
-      <c r="A103" s="10"/>
-      <c r="B103" s="10"/>
-      <c r="C103" s="10"/>
+      <c r="A103" s="9"/>
+      <c r="B103" s="9"/>
+      <c r="C103" s="9"/>
     </row>
     <row r="104" ht="12.0" customHeight="1">
-      <c r="A104" s="10"/>
-      <c r="B104" s="10"/>
-      <c r="C104" s="10"/>
+      <c r="A104" s="9"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="9"/>
     </row>
     <row r="105" ht="12.0" customHeight="1">
-      <c r="A105" s="10"/>
-      <c r="B105" s="10"/>
-      <c r="C105" s="10"/>
+      <c r="A105" s="9"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="9"/>
     </row>
     <row r="106" ht="12.0" customHeight="1">
-      <c r="A106" s="10"/>
-      <c r="B106" s="10"/>
-      <c r="C106" s="10"/>
+      <c r="A106" s="9"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="9"/>
     </row>
     <row r="107" ht="12.0" customHeight="1">
-      <c r="A107" s="10"/>
-      <c r="B107" s="10"/>
-      <c r="C107" s="10"/>
+      <c r="A107" s="9"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="9"/>
     </row>
     <row r="108" ht="12.0" customHeight="1">
-      <c r="A108" s="10"/>
-      <c r="B108" s="10"/>
-      <c r="C108" s="10"/>
+      <c r="A108" s="9"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
     </row>
     <row r="109" ht="12.0" customHeight="1">
-      <c r="A109" s="10"/>
-      <c r="B109" s="10"/>
-      <c r="C109" s="10"/>
+      <c r="A109" s="9"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
     </row>
     <row r="110" ht="12.0" customHeight="1">
-      <c r="A110" s="10"/>
-      <c r="B110" s="10"/>
-      <c r="C110" s="10"/>
+      <c r="A110" s="9"/>
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
     </row>
     <row r="111" ht="12.0" customHeight="1">
-      <c r="A111" s="10"/>
-      <c r="B111" s="10"/>
-      <c r="C111" s="10"/>
+      <c r="A111" s="9"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
     </row>
     <row r="112" ht="12.0" customHeight="1">
-      <c r="A112" s="10"/>
-      <c r="B112" s="10"/>
-      <c r="C112" s="10"/>
+      <c r="A112" s="9"/>
+      <c r="B112" s="9"/>
+      <c r="C112" s="9"/>
     </row>
     <row r="113" ht="12.0" customHeight="1">
-      <c r="A113" s="10"/>
-      <c r="B113" s="10"/>
-      <c r="C113" s="10"/>
+      <c r="A113" s="9"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
     </row>
     <row r="114" ht="12.0" customHeight="1">
-      <c r="A114" s="10"/>
-      <c r="B114" s="10"/>
-      <c r="C114" s="10"/>
+      <c r="A114" s="9"/>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9"/>
     </row>
     <row r="115" ht="12.0" customHeight="1">
-      <c r="A115" s="10"/>
-      <c r="B115" s="10"/>
-      <c r="C115" s="10"/>
+      <c r="A115" s="9"/>
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
     </row>
     <row r="116" ht="12.0" customHeight="1">
-      <c r="A116" s="10"/>
-      <c r="B116" s="10"/>
-      <c r="C116" s="10"/>
+      <c r="A116" s="9"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="9"/>
     </row>
     <row r="117" ht="12.0" customHeight="1">
-      <c r="A117" s="10"/>
-      <c r="B117" s="10"/>
-      <c r="C117" s="10"/>
+      <c r="A117" s="9"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="9"/>
     </row>
     <row r="118" ht="12.0" customHeight="1">
-      <c r="A118" s="10"/>
-      <c r="B118" s="10"/>
-      <c r="C118" s="10"/>
+      <c r="A118" s="9"/>
+      <c r="B118" s="9"/>
+      <c r="C118" s="9"/>
     </row>
     <row r="119" ht="12.0" customHeight="1">
-      <c r="A119" s="10"/>
-      <c r="B119" s="10"/>
-      <c r="C119" s="10"/>
+      <c r="A119" s="9"/>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
     </row>
     <row r="120" ht="15.75" customHeight="1"/>
     <row r="121" ht="15.75" customHeight="1"/>
@@ -9261,22 +9255,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="15"/>
+      <c r="F1" s="14"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
@@ -9301,8 +9295,8 @@
       <c r="A2" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="16"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="15"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
@@ -9327,11 +9321,11 @@
       <c r="Y2" s="7"/>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D3" s="7"/>
@@ -9358,11 +9352,11 @@
       <c r="Y3" s="7"/>
     </row>
     <row r="4">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7"/>
@@ -9389,11 +9383,11 @@
       <c r="Y4" s="7"/>
     </row>
     <row r="5">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>42</v>
       </c>
       <c r="D5" s="7"/>
@@ -9420,8 +9414,8 @@
       <c r="Y5" s="7"/>
     </row>
     <row r="6">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -9451,8 +9445,8 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9" t="s">
         <v>44</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -9482,8 +9476,8 @@
       <c r="Y7" s="7"/>
     </row>
     <row r="8">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10" t="s">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -9513,8 +9507,8 @@
       <c r="Y8" s="7"/>
     </row>
     <row r="9">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10" t="s">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -9544,11 +9538,11 @@
       <c r="Y9" s="7"/>
     </row>
     <row r="10">
-      <c r="A10" s="14"/>
-      <c r="B10" s="10" t="s">
+      <c r="A10" s="13"/>
+      <c r="B10" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="7"/>
@@ -9575,16 +9569,16 @@
       <c r="Y10" s="7"/>
     </row>
     <row r="11">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="17"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="16"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="16"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="15"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
@@ -9605,15 +9599,15 @@
       <c r="A12" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="16"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="15"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="16"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="15"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
@@ -9631,20 +9625,20 @@
       <c r="Y12" s="7"/>
     </row>
     <row r="13">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10" t="s">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="16"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="15"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
@@ -9662,20 +9656,20 @@
       <c r="Y13" s="7"/>
     </row>
     <row r="14">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10" t="s">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="16"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="15"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
@@ -9693,20 +9687,20 @@
       <c r="Y14" s="7"/>
     </row>
     <row r="15">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10" t="s">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>42</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="16"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="15"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
@@ -9724,20 +9718,20 @@
       <c r="Y15" s="7"/>
     </row>
     <row r="16">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10" t="s">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="7"/>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="17" t="s">
         <v>51</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="16"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="15"/>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
@@ -9755,8 +9749,8 @@
       <c r="Y16" s="7"/>
     </row>
     <row r="17">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10" t="s">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9" t="s">
         <v>44</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -9766,9 +9760,9 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="16"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="15"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
@@ -9786,8 +9780,8 @@
       <c r="Y17" s="7"/>
     </row>
     <row r="18">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10" t="s">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C18" s="6" t="s">
@@ -9797,9 +9791,9 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="16"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="15"/>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
@@ -9817,8 +9811,8 @@
       <c r="Y18" s="7"/>
     </row>
     <row r="19">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10" t="s">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C19" s="6" t="s">
@@ -9828,9 +9822,9 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="16"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="15"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
@@ -9848,20 +9842,20 @@
       <c r="Y19" s="7"/>
     </row>
     <row r="20">
-      <c r="A20" s="14"/>
-      <c r="B20" s="10" t="s">
+      <c r="A20" s="13"/>
+      <c r="B20" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="16"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="15"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
@@ -9878,17 +9872,17 @@
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
     </row>
-    <row r="21">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="17"/>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="16"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="16"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="15"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
@@ -9905,19 +9899,19 @@
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="16"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="15"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="16"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="15"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
@@ -9934,21 +9928,21 @@
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
     </row>
-    <row r="23">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10" t="s">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="16"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="15"/>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
       <c r="M23" s="7"/>
@@ -9965,21 +9959,21 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
     </row>
-    <row r="24">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10" t="s">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="16"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="15"/>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7"/>
@@ -9996,21 +9990,21 @@
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
     </row>
-    <row r="25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10" t="s">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="15" t="s">
         <v>42</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="16"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="15"/>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
@@ -10027,21 +10021,21 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
     </row>
-    <row r="26">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10" t="s">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="7"/>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="17" t="s">
         <v>53</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="16"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="15"/>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
       <c r="M26" s="7"/>
@@ -10058,9 +10052,9 @@
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
     </row>
-    <row r="27">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="7" t="s">
@@ -10070,9 +10064,9 @@
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="16"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="15"/>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
@@ -10089,9 +10083,9 @@
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
     </row>
-    <row r="28">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -10101,9 +10095,9 @@
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="16"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="15"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
       <c r="M28" s="7"/>
@@ -10120,9 +10114,9 @@
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
     </row>
-    <row r="29">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -10132,9 +10126,9 @@
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="16"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="15"/>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
       <c r="M29" s="7"/>
@@ -10151,21 +10145,21 @@
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
     </row>
-    <row r="30">
-      <c r="A30" s="14"/>
-      <c r="B30" s="10" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="13"/>
+      <c r="B30" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="16"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="15"/>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
@@ -10182,17 +10176,17 @@
       <c r="X30" s="7"/>
       <c r="Y30" s="7"/>
     </row>
-    <row r="31">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="17"/>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="16"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="16"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="15"/>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
       <c r="M31" s="7"/>
@@ -10209,19 +10203,19 @@
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
     </row>
-    <row r="32">
-      <c r="A32" s="19" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="16"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="15"/>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
       <c r="M32" s="7"/>
@@ -10238,21 +10232,21 @@
       <c r="X32" s="7"/>
       <c r="Y32" s="7"/>
     </row>
-    <row r="33">
-      <c r="A33" s="20"/>
-      <c r="B33" s="22" t="s">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="19"/>
+      <c r="B33" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="16"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="15"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
@@ -10269,21 +10263,21 @@
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
     </row>
-    <row r="34">
-      <c r="A34" s="20"/>
-      <c r="B34" s="22" t="s">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="19"/>
+      <c r="B34" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="16"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="15"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
@@ -10300,21 +10294,21 @@
       <c r="X34" s="7"/>
       <c r="Y34" s="7"/>
     </row>
-    <row r="35">
-      <c r="A35" s="20"/>
-      <c r="B35" s="22" t="s">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="19"/>
+      <c r="B35" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C35" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="16"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="15"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
@@ -10331,21 +10325,21 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
     </row>
-    <row r="36">
-      <c r="A36" s="20"/>
-      <c r="B36" s="22" t="s">
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="19"/>
+      <c r="B36" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="19" t="s">
+      <c r="C36" s="19"/>
+      <c r="D36" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="21"/>
+      <c r="E36" s="20"/>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="16"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="15"/>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
@@ -10362,21 +10356,21 @@
       <c r="X36" s="7"/>
       <c r="Y36" s="7"/>
     </row>
-    <row r="37">
-      <c r="A37" s="20"/>
-      <c r="B37" s="22" t="s">
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="19"/>
+      <c r="B37" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="16"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="15"/>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
@@ -10393,21 +10387,21 @@
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
     </row>
-    <row r="38">
-      <c r="A38" s="20"/>
-      <c r="B38" s="22" t="s">
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="19"/>
+      <c r="B38" s="21" t="s">
         <v>46</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="16"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="15"/>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
@@ -10424,21 +10418,21 @@
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
     </row>
-    <row r="39">
-      <c r="A39" s="20"/>
-      <c r="B39" s="22" t="s">
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="19"/>
+      <c r="B39" s="21" t="s">
         <v>48</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="16"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="15"/>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
@@ -10455,21 +10449,21 @@
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
     </row>
-    <row r="40">
-      <c r="A40" s="20"/>
-      <c r="B40" s="22" t="s">
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="19"/>
+      <c r="B40" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="16"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="15"/>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
@@ -10486,17 +10480,17 @@
       <c r="X40" s="7"/>
       <c r="Y40" s="7"/>
     </row>
-    <row r="41">
-      <c r="A41" s="14"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="17"/>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="16"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="16"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="15"/>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
@@ -10513,19 +10507,19 @@
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
     </row>
-    <row r="42">
-      <c r="A42" s="10" t="s">
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="10"/>
-      <c r="C42" s="11"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="10"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="11"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="10"/>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
@@ -10542,21 +10536,21 @@
       <c r="X42" s="7"/>
       <c r="Y42" s="7"/>
     </row>
-    <row r="43">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10" t="s">
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="10" t="s">
         <v>39</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="11"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="10"/>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
@@ -10573,21 +10567,21 @@
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
     </row>
-    <row r="44">
-      <c r="A44" s="10"/>
-      <c r="B44" s="10" t="s">
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="9"/>
+      <c r="B44" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="10" t="s">
         <v>41</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="11"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="10"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
@@ -10604,21 +10598,21 @@
       <c r="X44" s="7"/>
       <c r="Y44" s="7"/>
     </row>
-    <row r="45">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10" t="s">
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="10" t="s">
         <v>59</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="11"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="10"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
@@ -10635,21 +10629,21 @@
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
     </row>
-    <row r="46">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10" t="s">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="9"/>
+      <c r="B46" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10" t="s">
+      <c r="C46" s="9"/>
+      <c r="D46" s="9" t="s">
         <v>58</v>
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="11"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="10"/>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
@@ -10666,21 +10660,21 @@
       <c r="X46" s="7"/>
       <c r="Y46" s="7"/>
     </row>
-    <row r="47">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10" t="s">
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="9"/>
+      <c r="B47" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
-      <c r="H47" s="10"/>
+      <c r="H47" s="9"/>
       <c r="I47" s="4"/>
-      <c r="J47" s="23"/>
+      <c r="J47" s="22"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
@@ -10697,21 +10691,21 @@
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
     </row>
-    <row r="48">
-      <c r="A48" s="10"/>
-      <c r="B48" s="10" t="s">
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="9"/>
+      <c r="B48" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C48" s="24">
+      <c r="C48" s="23">
         <v>-1.0E20</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
-      <c r="H48" s="10"/>
+      <c r="H48" s="9"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="25"/>
+      <c r="J48" s="24"/>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
@@ -10728,9 +10722,9 @@
       <c r="X48" s="7"/>
       <c r="Y48" s="7"/>
     </row>
-    <row r="49">
-      <c r="A49" s="10"/>
-      <c r="B49" s="10" t="s">
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="9"/>
+      <c r="B49" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -10759,9 +10753,9 @@
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
     </row>
-    <row r="50">
-      <c r="A50" s="10"/>
-      <c r="B50" s="10" t="s">
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="9"/>
+      <c r="B50" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -10790,12 +10784,12 @@
       <c r="X50" s="7"/>
       <c r="Y50" s="7"/>
     </row>
-    <row r="51">
-      <c r="A51" s="10"/>
-      <c r="B51" s="23" t="s">
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="9"/>
+      <c r="B51" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C51" s="23"/>
+      <c r="C51" s="22"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3" t="s">
         <v>63</v>
@@ -10821,12 +10815,12 @@
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
     </row>
-    <row r="52">
-      <c r="A52" s="10"/>
-      <c r="B52" s="10" t="s">
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="9"/>
+      <c r="B52" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D52" s="7"/>
@@ -10852,10 +10846,10 @@
       <c r="X52" s="7"/>
       <c r="Y52" s="7"/>
     </row>
-    <row r="53">
-      <c r="A53" s="10"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="16"/>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="9"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="15"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
@@ -10879,12 +10873,12 @@
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
     </row>
-    <row r="54">
-      <c r="A54" s="10" t="s">
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B54" s="10"/>
-      <c r="C54" s="11"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="10"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
@@ -10908,12 +10902,12 @@
       <c r="X54" s="7"/>
       <c r="Y54" s="7"/>
     </row>
-    <row r="55">
-      <c r="A55" s="10"/>
-      <c r="B55" s="10" t="s">
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="9"/>
+      <c r="B55" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="10" t="s">
         <v>39</v>
       </c>
       <c r="D55" s="7"/>
@@ -10939,12 +10933,12 @@
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
     </row>
-    <row r="56">
-      <c r="A56" s="10"/>
-      <c r="B56" s="10" t="s">
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="9"/>
+      <c r="B56" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="10" t="s">
         <v>41</v>
       </c>
       <c r="D56" s="7"/>
@@ -10970,12 +10964,12 @@
       <c r="X56" s="7"/>
       <c r="Y56" s="7"/>
     </row>
-    <row r="57">
-      <c r="A57" s="10"/>
-      <c r="B57" s="10" t="s">
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="9"/>
+      <c r="B57" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D57" s="7"/>
@@ -11001,13 +10995,13 @@
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
     </row>
-    <row r="58">
-      <c r="A58" s="10"/>
-      <c r="B58" s="10" t="s">
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="9"/>
+      <c r="B58" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10" t="s">
+      <c r="C58" s="9"/>
+      <c r="D58" s="9" t="s">
         <v>64</v>
       </c>
       <c r="E58" s="7"/>
@@ -11032,12 +11026,12 @@
       <c r="X58" s="7"/>
       <c r="Y58" s="7"/>
     </row>
-    <row r="59">
-      <c r="A59" s="10"/>
-      <c r="B59" s="10" t="s">
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="9"/>
+      <c r="B59" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="10" t="s">
         <v>65</v>
       </c>
       <c r="D59" s="7"/>
@@ -11063,12 +11057,12 @@
       <c r="X59" s="7"/>
       <c r="Y59" s="7"/>
     </row>
-    <row r="60">
-      <c r="A60" s="10"/>
-      <c r="B60" s="10" t="s">
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="9"/>
+      <c r="B60" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C60" s="24">
+      <c r="C60" s="23">
         <v>-1.0E20</v>
       </c>
       <c r="D60" s="7"/>
@@ -11094,9 +11088,9 @@
       <c r="X60" s="7"/>
       <c r="Y60" s="7"/>
     </row>
-    <row r="61">
-      <c r="A61" s="10"/>
-      <c r="B61" s="10" t="s">
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="9"/>
+      <c r="B61" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -11125,9 +11119,9 @@
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
     </row>
-    <row r="62">
-      <c r="A62" s="10"/>
-      <c r="B62" s="10" t="s">
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="9"/>
+      <c r="B62" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -11156,12 +11150,12 @@
       <c r="X62" s="7"/>
       <c r="Y62" s="7"/>
     </row>
-    <row r="63">
-      <c r="A63" s="10"/>
-      <c r="B63" s="23" t="s">
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="9"/>
+      <c r="B63" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="23"/>
+      <c r="C63" s="22"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3" t="s">
         <v>63</v>
@@ -11187,12 +11181,12 @@
       <c r="X63" s="7"/>
       <c r="Y63" s="7"/>
     </row>
-    <row r="64">
-      <c r="A64" s="10"/>
-      <c r="B64" s="10" t="s">
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="9"/>
+      <c r="B64" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D64" s="7"/>
@@ -11218,10 +11212,10 @@
       <c r="X64" s="7"/>
       <c r="Y64" s="7"/>
     </row>
-    <row r="65">
-      <c r="A65" s="10"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="16"/>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="9"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="15"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
       <c r="F65" s="7"/>
@@ -11245,8 +11239,8 @@
       <c r="X65" s="7"/>
       <c r="Y65" s="7"/>
     </row>
-    <row r="66">
-      <c r="A66" s="26" t="s">
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="25" t="s">
         <v>66</v>
       </c>
       <c r="B66" s="4"/>
@@ -11274,12 +11268,12 @@
       <c r="X66" s="7"/>
       <c r="Y66" s="7"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="4"/>
       <c r="B67" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C67" s="22" t="s">
+      <c r="C67" s="21" t="s">
         <v>39</v>
       </c>
       <c r="D67" s="4"/>
@@ -11305,7 +11299,7 @@
       <c r="X67" s="7"/>
       <c r="Y67" s="7"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="4"/>
       <c r="B68" s="4" t="s">
         <v>40</v>
@@ -11336,12 +11330,12 @@
       <c r="X68" s="7"/>
       <c r="Y68" s="7"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C69" s="22" t="s">
+      <c r="C69" s="21" t="s">
         <v>56</v>
       </c>
       <c r="D69" s="4"/>
@@ -11367,13 +11361,13 @@
       <c r="X69" s="7"/>
       <c r="Y69" s="7"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26" t="s">
+      <c r="C70" s="25"/>
+      <c r="D70" s="25" t="s">
         <v>68</v>
       </c>
       <c r="E70" s="4"/>
@@ -11398,12 +11392,12 @@
       <c r="X70" s="7"/>
       <c r="Y70" s="7"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C71" s="27" t="s">
+      <c r="C71" s="25" t="s">
         <v>69</v>
       </c>
       <c r="D71" s="4"/>
@@ -11429,12 +11423,12 @@
       <c r="X71" s="7"/>
       <c r="Y71" s="7"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="4"/>
       <c r="B72" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C72" s="28">
+      <c r="C72" s="26">
         <v>-1.0E20</v>
       </c>
       <c r="D72" s="4"/>
@@ -11460,12 +11454,12 @@
       <c r="X72" s="7"/>
       <c r="Y72" s="7"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C73" s="22" t="s">
+      <c r="C73" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D73" s="4"/>
@@ -11491,12 +11485,12 @@
       <c r="X73" s="7"/>
       <c r="Y73" s="7"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="4"/>
       <c r="B74" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C74" s="22" t="s">
+      <c r="C74" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D74" s="4"/>
@@ -11522,14 +11516,14 @@
       <c r="X74" s="7"/>
       <c r="Y74" s="7"/>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="4"/>
-      <c r="B75" s="23" t="s">
+      <c r="B75" s="22" t="s">
         <v>62</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
-      <c r="E75" s="25" t="s">
+      <c r="E75" s="24" t="s">
         <v>63</v>
       </c>
       <c r="F75" s="7"/>
@@ -11553,7 +11547,7 @@
       <c r="X75" s="7"/>
       <c r="Y75" s="7"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="4"/>
       <c r="B76" s="4" t="s">
         <v>49</v>
@@ -11584,10 +11578,10 @@
       <c r="X76" s="7"/>
       <c r="Y76" s="7"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
-      <c r="C77" s="11"/>
+      <c r="C77" s="10"/>
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
       <c r="F77" s="7"/>
@@ -11611,12 +11605,12 @@
       <c r="X77" s="7"/>
       <c r="Y77" s="7"/>
     </row>
-    <row r="78">
-      <c r="A78" s="10" t="s">
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B78" s="10"/>
-      <c r="C78" s="11"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="10"/>
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
       <c r="F78" s="7"/>
@@ -11640,12 +11634,12 @@
       <c r="X78" s="7"/>
       <c r="Y78" s="7"/>
     </row>
-    <row r="79">
-      <c r="A79" s="10"/>
-      <c r="B79" s="10" t="s">
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="9"/>
+      <c r="B79" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C79" s="10" t="s">
         <v>39</v>
       </c>
       <c r="D79" s="7"/>
@@ -11671,12 +11665,12 @@
       <c r="X79" s="7"/>
       <c r="Y79" s="7"/>
     </row>
-    <row r="80">
-      <c r="A80" s="10"/>
-      <c r="B80" s="10" t="s">
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="9"/>
+      <c r="B80" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C80" s="10" t="s">
         <v>67</v>
       </c>
       <c r="D80" s="7"/>
@@ -11702,12 +11696,12 @@
       <c r="X80" s="7"/>
       <c r="Y80" s="7"/>
     </row>
-    <row r="81">
-      <c r="A81" s="10"/>
-      <c r="B81" s="10" t="s">
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="9"/>
+      <c r="B81" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C81" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D81" s="7"/>
@@ -11733,13 +11727,13 @@
       <c r="X81" s="7"/>
       <c r="Y81" s="7"/>
     </row>
-    <row r="82">
-      <c r="A82" s="10"/>
-      <c r="B82" s="10" t="s">
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="9"/>
+      <c r="B82" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C82" s="10"/>
-      <c r="D82" s="10" t="s">
+      <c r="C82" s="9"/>
+      <c r="D82" s="9" t="s">
         <v>70</v>
       </c>
       <c r="E82" s="7"/>
@@ -11764,12 +11758,12 @@
       <c r="X82" s="7"/>
       <c r="Y82" s="7"/>
     </row>
-    <row r="83">
-      <c r="A83" s="10"/>
-      <c r="B83" s="10" t="s">
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="9"/>
+      <c r="B83" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C83" s="11" t="s">
+      <c r="C83" s="10" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="7"/>
@@ -11795,12 +11789,12 @@
       <c r="X83" s="7"/>
       <c r="Y83" s="7"/>
     </row>
-    <row r="84">
-      <c r="A84" s="10"/>
-      <c r="B84" s="10" t="s">
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="9"/>
+      <c r="B84" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C84" s="24">
+      <c r="C84" s="23">
         <v>-1.0E20</v>
       </c>
       <c r="D84" s="7"/>
@@ -11826,9 +11820,9 @@
       <c r="X84" s="7"/>
       <c r="Y84" s="7"/>
     </row>
-    <row r="85">
-      <c r="A85" s="10"/>
-      <c r="B85" s="10" t="s">
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="9"/>
+      <c r="B85" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -11857,9 +11851,9 @@
       <c r="X85" s="7"/>
       <c r="Y85" s="7"/>
     </row>
-    <row r="86">
-      <c r="A86" s="10"/>
-      <c r="B86" s="10" t="s">
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="9"/>
+      <c r="B86" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -11888,12 +11882,12 @@
       <c r="X86" s="7"/>
       <c r="Y86" s="7"/>
     </row>
-    <row r="87">
-      <c r="A87" s="10"/>
-      <c r="B87" s="23" t="s">
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="9"/>
+      <c r="B87" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C87" s="23"/>
+      <c r="C87" s="22"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3" t="s">
         <v>63</v>
@@ -11919,12 +11913,12 @@
       <c r="X87" s="7"/>
       <c r="Y87" s="7"/>
     </row>
-    <row r="88">
-      <c r="A88" s="10"/>
-      <c r="B88" s="10" t="s">
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="9"/>
+      <c r="B88" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D88" s="7"/>
@@ -11950,10 +11944,10 @@
       <c r="X88" s="7"/>
       <c r="Y88" s="7"/>
     </row>
-    <row r="89">
-      <c r="A89" s="10"/>
-      <c r="B89" s="10"/>
-      <c r="C89" s="16"/>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="9"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="15"/>
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
       <c r="F89" s="7"/>
@@ -11977,12 +11971,12 @@
       <c r="X89" s="7"/>
       <c r="Y89" s="7"/>
     </row>
-    <row r="90">
-      <c r="A90" s="10" t="s">
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B90" s="10"/>
-      <c r="C90" s="11"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="10"/>
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
       <c r="F90" s="7"/>
@@ -12006,12 +12000,12 @@
       <c r="X90" s="7"/>
       <c r="Y90" s="7"/>
     </row>
-    <row r="91">
-      <c r="A91" s="10"/>
-      <c r="B91" s="10" t="s">
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="9"/>
+      <c r="B91" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C91" s="10" t="s">
         <v>39</v>
       </c>
       <c r="D91" s="7"/>
@@ -12037,12 +12031,12 @@
       <c r="X91" s="7"/>
       <c r="Y91" s="7"/>
     </row>
-    <row r="92">
-      <c r="A92" s="10"/>
-      <c r="B92" s="10" t="s">
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="9"/>
+      <c r="B92" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="C92" s="10" t="s">
         <v>67</v>
       </c>
       <c r="D92" s="7"/>
@@ -12068,12 +12062,12 @@
       <c r="X92" s="7"/>
       <c r="Y92" s="7"/>
     </row>
-    <row r="93">
-      <c r="A93" s="10"/>
-      <c r="B93" s="10" t="s">
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="9"/>
+      <c r="B93" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C93" s="11" t="s">
+      <c r="C93" s="10" t="s">
         <v>74</v>
       </c>
       <c r="D93" s="7"/>
@@ -12099,13 +12093,13 @@
       <c r="X93" s="7"/>
       <c r="Y93" s="7"/>
     </row>
-    <row r="94">
-      <c r="A94" s="10"/>
-      <c r="B94" s="10" t="s">
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="9"/>
+      <c r="B94" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C94" s="10"/>
-      <c r="D94" s="10" t="s">
+      <c r="C94" s="9"/>
+      <c r="D94" s="9" t="s">
         <v>73</v>
       </c>
       <c r="E94" s="7"/>
@@ -12130,12 +12124,12 @@
       <c r="X94" s="7"/>
       <c r="Y94" s="7"/>
     </row>
-    <row r="95">
-      <c r="A95" s="10"/>
-      <c r="B95" s="10" t="s">
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="9"/>
+      <c r="B95" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C95" s="11" t="s">
+      <c r="C95" s="10" t="s">
         <v>75</v>
       </c>
       <c r="D95" s="7"/>
@@ -12161,12 +12155,12 @@
       <c r="X95" s="7"/>
       <c r="Y95" s="7"/>
     </row>
-    <row r="96">
-      <c r="A96" s="10"/>
-      <c r="B96" s="10" t="s">
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="9"/>
+      <c r="B96" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C96" s="24">
+      <c r="C96" s="23">
         <v>-1.0E20</v>
       </c>
       <c r="D96" s="7"/>
@@ -12192,9 +12186,9 @@
       <c r="X96" s="7"/>
       <c r="Y96" s="7"/>
     </row>
-    <row r="97">
-      <c r="A97" s="10"/>
-      <c r="B97" s="10" t="s">
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="9"/>
+      <c r="B97" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -12223,9 +12217,9 @@
       <c r="X97" s="7"/>
       <c r="Y97" s="7"/>
     </row>
-    <row r="98">
-      <c r="A98" s="10"/>
-      <c r="B98" s="10" t="s">
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="9"/>
+      <c r="B98" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -12254,12 +12248,12 @@
       <c r="X98" s="7"/>
       <c r="Y98" s="7"/>
     </row>
-    <row r="99">
-      <c r="A99" s="10"/>
-      <c r="B99" s="23" t="s">
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="9"/>
+      <c r="B99" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C99" s="23"/>
+      <c r="C99" s="22"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3" t="s">
         <v>63</v>
@@ -12285,12 +12279,12 @@
       <c r="X99" s="7"/>
       <c r="Y99" s="7"/>
     </row>
-    <row r="100">
-      <c r="A100" s="10"/>
-      <c r="B100" s="10" t="s">
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="9"/>
+      <c r="B100" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C100" s="11" t="s">
+      <c r="C100" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D100" s="7"/>
@@ -12316,10 +12310,10 @@
       <c r="X100" s="7"/>
       <c r="Y100" s="7"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
-      <c r="C101" s="11"/>
+      <c r="C101" s="10"/>
       <c r="D101" s="7"/>
       <c r="E101" s="7"/>
       <c r="F101" s="7"/>
@@ -12343,12 +12337,12 @@
       <c r="X101" s="7"/>
       <c r="Y101" s="7"/>
     </row>
-    <row r="102">
-      <c r="A102" s="10" t="s">
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B102" s="10"/>
-      <c r="C102" s="11"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="10"/>
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
       <c r="F102" s="7"/>
@@ -12372,12 +12366,12 @@
       <c r="X102" s="7"/>
       <c r="Y102" s="7"/>
     </row>
-    <row r="103">
-      <c r="A103" s="10"/>
-      <c r="B103" s="10" t="s">
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="9"/>
+      <c r="B103" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="C103" s="10" t="s">
         <v>39</v>
       </c>
       <c r="D103" s="7"/>
@@ -12403,12 +12397,12 @@
       <c r="X103" s="7"/>
       <c r="Y103" s="7"/>
     </row>
-    <row r="104">
-      <c r="A104" s="10"/>
-      <c r="B104" s="10" t="s">
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="9"/>
+      <c r="B104" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="11" t="s">
+      <c r="C104" s="10" t="s">
         <v>67</v>
       </c>
       <c r="D104" s="7"/>
@@ -12434,12 +12428,12 @@
       <c r="X104" s="7"/>
       <c r="Y104" s="7"/>
     </row>
-    <row r="105">
-      <c r="A105" s="10"/>
-      <c r="B105" s="10" t="s">
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="9"/>
+      <c r="B105" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C105" s="11" t="s">
+      <c r="C105" s="10" t="s">
         <v>77</v>
       </c>
       <c r="D105" s="7"/>
@@ -12465,13 +12459,13 @@
       <c r="X105" s="7"/>
       <c r="Y105" s="7"/>
     </row>
-    <row r="106">
-      <c r="A106" s="10"/>
-      <c r="B106" s="10" t="s">
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="9"/>
+      <c r="B106" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C106" s="10"/>
-      <c r="D106" s="10" t="s">
+      <c r="C106" s="9"/>
+      <c r="D106" s="9" t="s">
         <v>76</v>
       </c>
       <c r="E106" s="7"/>
@@ -12496,12 +12490,12 @@
       <c r="X106" s="7"/>
       <c r="Y106" s="7"/>
     </row>
-    <row r="107">
-      <c r="A107" s="10"/>
-      <c r="B107" s="10" t="s">
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="9"/>
+      <c r="B107" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="C107" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D107" s="7"/>
@@ -12527,12 +12521,12 @@
       <c r="X107" s="7"/>
       <c r="Y107" s="7"/>
     </row>
-    <row r="108">
-      <c r="A108" s="10"/>
-      <c r="B108" s="10" t="s">
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="9"/>
+      <c r="B108" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C108" s="24">
+      <c r="C108" s="23">
         <v>-1.0E20</v>
       </c>
       <c r="D108" s="7"/>
@@ -12558,9 +12552,9 @@
       <c r="X108" s="7"/>
       <c r="Y108" s="7"/>
     </row>
-    <row r="109">
-      <c r="A109" s="10"/>
-      <c r="B109" s="10" t="s">
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="9"/>
+      <c r="B109" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -12589,9 +12583,9 @@
       <c r="X109" s="7"/>
       <c r="Y109" s="7"/>
     </row>
-    <row r="110">
-      <c r="A110" s="10"/>
-      <c r="B110" s="10" t="s">
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="9"/>
+      <c r="B110" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -12620,12 +12614,12 @@
       <c r="X110" s="7"/>
       <c r="Y110" s="7"/>
     </row>
-    <row r="111">
-      <c r="A111" s="10"/>
-      <c r="B111" s="23" t="s">
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="9"/>
+      <c r="B111" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C111" s="23"/>
+      <c r="C111" s="22"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3" t="s">
         <v>63</v>
@@ -12651,12 +12645,12 @@
       <c r="X111" s="7"/>
       <c r="Y111" s="7"/>
     </row>
-    <row r="112">
-      <c r="A112" s="10"/>
-      <c r="B112" s="10" t="s">
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="9"/>
+      <c r="B112" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C112" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D112" s="7"/>
@@ -12682,10 +12676,10 @@
       <c r="X112" s="7"/>
       <c r="Y112" s="7"/>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
-      <c r="C113" s="11"/>
+      <c r="C113" s="10"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7"/>
       <c r="F113" s="7"/>
@@ -12709,12 +12703,12 @@
       <c r="X113" s="7"/>
       <c r="Y113" s="7"/>
     </row>
-    <row r="114">
-      <c r="A114" s="10" t="s">
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B114" s="10"/>
-      <c r="C114" s="11"/>
+      <c r="B114" s="9"/>
+      <c r="C114" s="10"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7"/>
       <c r="F114" s="7"/>
@@ -12738,12 +12732,12 @@
       <c r="X114" s="7"/>
       <c r="Y114" s="7"/>
     </row>
-    <row r="115">
-      <c r="A115" s="10"/>
-      <c r="B115" s="10" t="s">
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="9"/>
+      <c r="B115" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C115" s="11" t="s">
+      <c r="C115" s="10" t="s">
         <v>39</v>
       </c>
       <c r="D115" s="7"/>
@@ -12769,12 +12763,12 @@
       <c r="X115" s="7"/>
       <c r="Y115" s="7"/>
     </row>
-    <row r="116">
-      <c r="A116" s="10"/>
-      <c r="B116" s="10" t="s">
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="9"/>
+      <c r="B116" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C116" s="11" t="s">
+      <c r="C116" s="10" t="s">
         <v>67</v>
       </c>
       <c r="D116" s="7"/>
@@ -12800,12 +12794,12 @@
       <c r="X116" s="7"/>
       <c r="Y116" s="7"/>
     </row>
-    <row r="117">
-      <c r="A117" s="10"/>
-      <c r="B117" s="10" t="s">
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="9"/>
+      <c r="B117" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C117" s="11" t="s">
+      <c r="C117" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D117" s="7"/>
@@ -12831,13 +12825,13 @@
       <c r="X117" s="7"/>
       <c r="Y117" s="7"/>
     </row>
-    <row r="118">
-      <c r="A118" s="10"/>
-      <c r="B118" s="10" t="s">
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="9"/>
+      <c r="B118" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C118" s="10"/>
-      <c r="D118" s="10" t="s">
+      <c r="C118" s="9"/>
+      <c r="D118" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E118" s="7"/>
@@ -12862,12 +12856,12 @@
       <c r="X118" s="7"/>
       <c r="Y118" s="7"/>
     </row>
-    <row r="119">
-      <c r="A119" s="10"/>
-      <c r="B119" s="10" t="s">
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="9"/>
+      <c r="B119" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C119" s="11" t="s">
+      <c r="C119" s="10" t="s">
         <v>81</v>
       </c>
       <c r="D119" s="7"/>
@@ -12893,12 +12887,12 @@
       <c r="X119" s="7"/>
       <c r="Y119" s="7"/>
     </row>
-    <row r="120">
-      <c r="A120" s="10"/>
-      <c r="B120" s="10" t="s">
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="9"/>
+      <c r="B120" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C120" s="24">
+      <c r="C120" s="23">
         <v>-1.0E20</v>
       </c>
       <c r="D120" s="7"/>
@@ -12924,9 +12918,9 @@
       <c r="X120" s="7"/>
       <c r="Y120" s="7"/>
     </row>
-    <row r="121">
-      <c r="A121" s="10"/>
-      <c r="B121" s="10" t="s">
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="9"/>
+      <c r="B121" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -12955,9 +12949,9 @@
       <c r="X121" s="7"/>
       <c r="Y121" s="7"/>
     </row>
-    <row r="122">
-      <c r="A122" s="10"/>
-      <c r="B122" s="10" t="s">
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="9"/>
+      <c r="B122" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -12986,12 +12980,12 @@
       <c r="X122" s="7"/>
       <c r="Y122" s="7"/>
     </row>
-    <row r="123">
-      <c r="A123" s="10"/>
-      <c r="B123" s="23" t="s">
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="9"/>
+      <c r="B123" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C123" s="23"/>
+      <c r="C123" s="22"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3" t="s">
         <v>63</v>
@@ -13017,12 +13011,12 @@
       <c r="X123" s="7"/>
       <c r="Y123" s="7"/>
     </row>
-    <row r="124">
-      <c r="A124" s="10"/>
-      <c r="B124" s="10" t="s">
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="9"/>
+      <c r="B124" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="C124" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D124" s="7"/>
@@ -13048,10 +13042,10 @@
       <c r="X124" s="7"/>
       <c r="Y124" s="7"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
-      <c r="C125" s="11"/>
+      <c r="C125" s="10"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
       <c r="F125" s="7"/>
@@ -13075,12 +13069,12 @@
       <c r="X125" s="7"/>
       <c r="Y125" s="7"/>
     </row>
-    <row r="126">
-      <c r="A126" s="10" t="s">
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B126" s="10"/>
-      <c r="C126" s="16"/>
+      <c r="B126" s="9"/>
+      <c r="C126" s="15"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
       <c r="F126" s="7"/>
@@ -13104,12 +13098,12 @@
       <c r="X126" s="7"/>
       <c r="Y126" s="7"/>
     </row>
-    <row r="127">
-      <c r="A127" s="10"/>
-      <c r="B127" s="10" t="s">
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="9"/>
+      <c r="B127" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C127" s="11" t="s">
+      <c r="C127" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D127" s="7"/>
@@ -13135,12 +13129,12 @@
       <c r="X127" s="7"/>
       <c r="Y127" s="7"/>
     </row>
-    <row r="128">
-      <c r="A128" s="10"/>
-      <c r="B128" s="10" t="s">
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="A128" s="9"/>
+      <c r="B128" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C128" s="11" t="s">
+      <c r="C128" s="10" t="s">
         <v>67</v>
       </c>
       <c r="D128" s="7"/>
@@ -13166,12 +13160,12 @@
       <c r="X128" s="7"/>
       <c r="Y128" s="7"/>
     </row>
-    <row r="129">
-      <c r="A129" s="10"/>
-      <c r="B129" s="10" t="s">
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="9"/>
+      <c r="B129" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C129" s="11">
+      <c r="C129" s="10">
         <v>1.0</v>
       </c>
       <c r="D129" s="7"/>
@@ -13197,12 +13191,12 @@
       <c r="X129" s="7"/>
       <c r="Y129" s="7"/>
     </row>
-    <row r="130">
-      <c r="A130" s="10"/>
-      <c r="B130" s="10" t="s">
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="9"/>
+      <c r="B130" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C130" s="11"/>
+      <c r="C130" s="10"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
       <c r="F130" s="7"/>
@@ -13226,12 +13220,12 @@
       <c r="X130" s="7"/>
       <c r="Y130" s="7"/>
     </row>
-    <row r="131">
-      <c r="A131" s="10"/>
-      <c r="B131" s="10" t="s">
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="9"/>
+      <c r="B131" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C131" s="11" t="s">
+      <c r="C131" s="10" t="s">
         <v>84</v>
       </c>
       <c r="D131" s="7"/>
@@ -13257,12 +13251,12 @@
       <c r="X131" s="7"/>
       <c r="Y131" s="7"/>
     </row>
-    <row r="132">
-      <c r="A132" s="10"/>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="9"/>
       <c r="B132" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C132" s="23" t="s">
+      <c r="C132" s="22" t="s">
         <v>86</v>
       </c>
       <c r="D132" s="7"/>
@@ -13288,12 +13282,12 @@
       <c r="X132" s="7"/>
       <c r="Y132" s="7"/>
     </row>
-    <row r="133">
-      <c r="A133" s="10"/>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="9"/>
       <c r="B133" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C133" s="25" t="s">
+      <c r="C133" s="24" t="s">
         <v>88</v>
       </c>
       <c r="D133" s="7"/>
@@ -13322,7 +13316,7 @@
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
-      <c r="C134" s="11"/>
+      <c r="C134" s="10"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
       <c r="F134" s="7"/>
@@ -13349,7 +13343,7 @@
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
-      <c r="C135" s="11"/>
+      <c r="C135" s="10"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
       <c r="F135" s="7"/>
@@ -13376,7 +13370,7 @@
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
-      <c r="C136" s="11"/>
+      <c r="C136" s="10"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7"/>
       <c r="F136" s="7"/>
@@ -13403,7 +13397,7 @@
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
-      <c r="C137" s="11"/>
+      <c r="C137" s="10"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
       <c r="F137" s="7"/>
@@ -13430,7 +13424,7 @@
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
-      <c r="C138" s="11"/>
+      <c r="C138" s="10"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
       <c r="F138" s="7"/>
@@ -13457,7 +13451,7 @@
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
-      <c r="C139" s="11"/>
+      <c r="C139" s="10"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7"/>
       <c r="F139" s="7"/>
@@ -13484,7 +13478,7 @@
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
-      <c r="C140" s="11"/>
+      <c r="C140" s="10"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7"/>
       <c r="F140" s="7"/>
@@ -13511,7 +13505,7 @@
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
-      <c r="C141" s="11"/>
+      <c r="C141" s="10"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7"/>
       <c r="F141" s="7"/>
@@ -13538,7 +13532,7 @@
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
-      <c r="C142" s="11"/>
+      <c r="C142" s="10"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7"/>
       <c r="F142" s="7"/>
@@ -13565,7 +13559,7 @@
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
-      <c r="C143" s="11"/>
+      <c r="C143" s="10"/>
       <c r="D143" s="7"/>
       <c r="E143" s="7"/>
       <c r="F143" s="7"/>
@@ -13592,7 +13586,7 @@
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
-      <c r="C144" s="11"/>
+      <c r="C144" s="10"/>
       <c r="D144" s="7"/>
       <c r="E144" s="7"/>
       <c r="F144" s="7"/>
@@ -13619,7 +13613,7 @@
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
-      <c r="C145" s="11"/>
+      <c r="C145" s="10"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7"/>
       <c r="F145" s="7"/>
@@ -13646,7 +13640,7 @@
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
-      <c r="C146" s="11"/>
+      <c r="C146" s="10"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7"/>
       <c r="F146" s="7"/>
@@ -13673,7 +13667,7 @@
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
-      <c r="C147" s="11"/>
+      <c r="C147" s="10"/>
       <c r="D147" s="7"/>
       <c r="E147" s="7"/>
       <c r="F147" s="7"/>
@@ -13700,7 +13694,7 @@
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
-      <c r="C148" s="11"/>
+      <c r="C148" s="10"/>
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
       <c r="F148" s="7"/>
@@ -13727,7 +13721,7 @@
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
-      <c r="C149" s="11"/>
+      <c r="C149" s="10"/>
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
       <c r="F149" s="7"/>
@@ -13754,7 +13748,7 @@
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
-      <c r="C150" s="11"/>
+      <c r="C150" s="10"/>
       <c r="D150" s="7"/>
       <c r="E150" s="7"/>
       <c r="F150" s="7"/>
@@ -13781,7 +13775,7 @@
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
-      <c r="C151" s="11"/>
+      <c r="C151" s="10"/>
       <c r="D151" s="7"/>
       <c r="E151" s="7"/>
       <c r="F151" s="7"/>
@@ -13808,7 +13802,7 @@
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
-      <c r="C152" s="11"/>
+      <c r="C152" s="10"/>
       <c r="D152" s="7"/>
       <c r="E152" s="7"/>
       <c r="F152" s="7"/>
@@ -13835,7 +13829,7 @@
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="7"/>
       <c r="B153" s="7"/>
-      <c r="C153" s="11"/>
+      <c r="C153" s="10"/>
       <c r="D153" s="7"/>
       <c r="E153" s="7"/>
       <c r="F153" s="7"/>
@@ -13862,7 +13856,7 @@
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
-      <c r="C154" s="11"/>
+      <c r="C154" s="10"/>
       <c r="D154" s="7"/>
       <c r="E154" s="7"/>
       <c r="F154" s="7"/>
@@ -13889,7 +13883,7 @@
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="7"/>
       <c r="B155" s="7"/>
-      <c r="C155" s="11"/>
+      <c r="C155" s="10"/>
       <c r="D155" s="7"/>
       <c r="E155" s="7"/>
       <c r="F155" s="7"/>
@@ -13916,7 +13910,7 @@
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
-      <c r="C156" s="11"/>
+      <c r="C156" s="10"/>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
       <c r="F156" s="7"/>
@@ -13943,7 +13937,7 @@
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="7"/>
       <c r="B157" s="7"/>
-      <c r="C157" s="11"/>
+      <c r="C157" s="10"/>
       <c r="D157" s="7"/>
       <c r="E157" s="7"/>
       <c r="F157" s="7"/>
@@ -13970,7 +13964,7 @@
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="7"/>
       <c r="B158" s="7"/>
-      <c r="C158" s="11"/>
+      <c r="C158" s="10"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
       <c r="F158" s="7"/>
@@ -13997,7 +13991,7 @@
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="7"/>
       <c r="B159" s="7"/>
-      <c r="C159" s="11"/>
+      <c r="C159" s="10"/>
       <c r="D159" s="7"/>
       <c r="E159" s="7"/>
       <c r="F159" s="7"/>
@@ -14024,7 +14018,7 @@
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
-      <c r="C160" s="11"/>
+      <c r="C160" s="10"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7"/>
       <c r="F160" s="7"/>
@@ -14051,7 +14045,7 @@
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="7"/>
       <c r="B161" s="7"/>
-      <c r="C161" s="11"/>
+      <c r="C161" s="10"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7"/>
       <c r="F161" s="7"/>
@@ -14078,7 +14072,7 @@
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
-      <c r="C162" s="11"/>
+      <c r="C162" s="10"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7"/>
       <c r="F162" s="7"/>
@@ -14105,7 +14099,7 @@
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="7"/>
       <c r="B163" s="7"/>
-      <c r="C163" s="11"/>
+      <c r="C163" s="10"/>
       <c r="D163" s="7"/>
       <c r="E163" s="7"/>
       <c r="F163" s="7"/>
@@ -14132,7 +14126,7 @@
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
-      <c r="C164" s="11"/>
+      <c r="C164" s="10"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7"/>
       <c r="F164" s="7"/>
@@ -14159,7 +14153,7 @@
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="7"/>
       <c r="B165" s="7"/>
-      <c r="C165" s="11"/>
+      <c r="C165" s="10"/>
       <c r="D165" s="7"/>
       <c r="E165" s="7"/>
       <c r="F165" s="7"/>
@@ -14186,7 +14180,7 @@
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
-      <c r="C166" s="11"/>
+      <c r="C166" s="10"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7"/>
       <c r="F166" s="7"/>
@@ -14213,7 +14207,7 @@
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="7"/>
       <c r="B167" s="7"/>
-      <c r="C167" s="11"/>
+      <c r="C167" s="10"/>
       <c r="D167" s="7"/>
       <c r="E167" s="7"/>
       <c r="F167" s="7"/>
@@ -14240,7 +14234,7 @@
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="7"/>
       <c r="B168" s="7"/>
-      <c r="C168" s="11"/>
+      <c r="C168" s="10"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
       <c r="F168" s="7"/>
@@ -14267,7 +14261,7 @@
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="7"/>
       <c r="B169" s="7"/>
-      <c r="C169" s="11"/>
+      <c r="C169" s="10"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
       <c r="F169" s="7"/>
@@ -14294,7 +14288,7 @@
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="7"/>
       <c r="B170" s="7"/>
-      <c r="C170" s="11"/>
+      <c r="C170" s="10"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7"/>
       <c r="F170" s="7"/>
@@ -14321,7 +14315,7 @@
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="7"/>
       <c r="B171" s="7"/>
-      <c r="C171" s="11"/>
+      <c r="C171" s="10"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
       <c r="F171" s="7"/>
@@ -14348,7 +14342,7 @@
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="7"/>
       <c r="B172" s="7"/>
-      <c r="C172" s="11"/>
+      <c r="C172" s="10"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
       <c r="F172" s="7"/>
@@ -14375,7 +14369,7 @@
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="7"/>
       <c r="B173" s="7"/>
-      <c r="C173" s="11"/>
+      <c r="C173" s="10"/>
       <c r="D173" s="7"/>
       <c r="E173" s="7"/>
       <c r="F173" s="7"/>
@@ -14402,7 +14396,7 @@
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="7"/>
       <c r="B174" s="7"/>
-      <c r="C174" s="11"/>
+      <c r="C174" s="10"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7"/>
       <c r="F174" s="7"/>
@@ -14429,7 +14423,7 @@
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="7"/>
       <c r="B175" s="7"/>
-      <c r="C175" s="11"/>
+      <c r="C175" s="10"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
       <c r="F175" s="7"/>
@@ -14456,7 +14450,7 @@
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="7"/>
       <c r="B176" s="7"/>
-      <c r="C176" s="11"/>
+      <c r="C176" s="10"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7"/>
       <c r="F176" s="7"/>
@@ -14483,7 +14477,7 @@
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="7"/>
       <c r="B177" s="7"/>
-      <c r="C177" s="11"/>
+      <c r="C177" s="10"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7"/>
       <c r="F177" s="7"/>
@@ -14510,7 +14504,7 @@
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="7"/>
       <c r="B178" s="7"/>
-      <c r="C178" s="11"/>
+      <c r="C178" s="10"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7"/>
       <c r="F178" s="7"/>
@@ -14537,7 +14531,7 @@
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="7"/>
       <c r="B179" s="7"/>
-      <c r="C179" s="11"/>
+      <c r="C179" s="10"/>
       <c r="D179" s="7"/>
       <c r="E179" s="7"/>
       <c r="F179" s="7"/>
@@ -14564,7 +14558,7 @@
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="7"/>
       <c r="B180" s="7"/>
-      <c r="C180" s="11"/>
+      <c r="C180" s="10"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7"/>
       <c r="F180" s="7"/>
@@ -14591,7 +14585,7 @@
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="7"/>
       <c r="B181" s="7"/>
-      <c r="C181" s="11"/>
+      <c r="C181" s="10"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7"/>
       <c r="F181" s="7"/>
@@ -14618,7 +14612,7 @@
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="7"/>
       <c r="B182" s="7"/>
-      <c r="C182" s="11"/>
+      <c r="C182" s="10"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7"/>
       <c r="F182" s="7"/>
@@ -14645,7 +14639,7 @@
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="7"/>
       <c r="B183" s="7"/>
-      <c r="C183" s="11"/>
+      <c r="C183" s="10"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7"/>
       <c r="F183" s="7"/>
@@ -14672,7 +14666,7 @@
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
-      <c r="C184" s="11"/>
+      <c r="C184" s="10"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
@@ -14699,7 +14693,7 @@
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="7"/>
       <c r="B185" s="7"/>
-      <c r="C185" s="11"/>
+      <c r="C185" s="10"/>
       <c r="D185" s="7"/>
       <c r="E185" s="7"/>
       <c r="F185" s="7"/>
@@ -14726,7 +14720,7 @@
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="7"/>
       <c r="B186" s="7"/>
-      <c r="C186" s="11"/>
+      <c r="C186" s="10"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
@@ -14753,7 +14747,7 @@
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="7"/>
       <c r="B187" s="7"/>
-      <c r="C187" s="11"/>
+      <c r="C187" s="10"/>
       <c r="D187" s="7"/>
       <c r="E187" s="7"/>
       <c r="F187" s="7"/>
@@ -14780,7 +14774,7 @@
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="7"/>
       <c r="B188" s="7"/>
-      <c r="C188" s="11"/>
+      <c r="C188" s="10"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7"/>
       <c r="F188" s="7"/>
@@ -14807,7 +14801,7 @@
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="7"/>
       <c r="B189" s="7"/>
-      <c r="C189" s="11"/>
+      <c r="C189" s="10"/>
       <c r="D189" s="7"/>
       <c r="E189" s="7"/>
       <c r="F189" s="7"/>
@@ -14834,7 +14828,7 @@
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="7"/>
       <c r="B190" s="7"/>
-      <c r="C190" s="11"/>
+      <c r="C190" s="10"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7"/>
       <c r="F190" s="7"/>
@@ -14861,7 +14855,7 @@
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="7"/>
       <c r="B191" s="7"/>
-      <c r="C191" s="11"/>
+      <c r="C191" s="10"/>
       <c r="D191" s="7"/>
       <c r="E191" s="7"/>
       <c r="F191" s="7"/>
@@ -14888,7 +14882,7 @@
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="7"/>
       <c r="B192" s="7"/>
-      <c r="C192" s="11"/>
+      <c r="C192" s="10"/>
       <c r="D192" s="7"/>
       <c r="E192" s="7"/>
       <c r="F192" s="7"/>
@@ -14915,7 +14909,7 @@
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="7"/>
       <c r="B193" s="7"/>
-      <c r="C193" s="11"/>
+      <c r="C193" s="10"/>
       <c r="D193" s="7"/>
       <c r="E193" s="7"/>
       <c r="F193" s="7"/>
@@ -14942,7 +14936,7 @@
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="7"/>
       <c r="B194" s="7"/>
-      <c r="C194" s="11"/>
+      <c r="C194" s="10"/>
       <c r="D194" s="7"/>
       <c r="E194" s="7"/>
       <c r="F194" s="7"/>
@@ -14969,7 +14963,7 @@
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="7"/>
       <c r="B195" s="7"/>
-      <c r="C195" s="11"/>
+      <c r="C195" s="10"/>
       <c r="D195" s="7"/>
       <c r="E195" s="7"/>
       <c r="F195" s="7"/>
@@ -14996,7 +14990,7 @@
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="7"/>
       <c r="B196" s="7"/>
-      <c r="C196" s="11"/>
+      <c r="C196" s="10"/>
       <c r="D196" s="7"/>
       <c r="E196" s="7"/>
       <c r="F196" s="7"/>
@@ -15023,7 +15017,7 @@
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="7"/>
       <c r="B197" s="7"/>
-      <c r="C197" s="11"/>
+      <c r="C197" s="10"/>
       <c r="D197" s="7"/>
       <c r="E197" s="7"/>
       <c r="F197" s="7"/>
@@ -15050,7 +15044,7 @@
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="7"/>
       <c r="B198" s="7"/>
-      <c r="C198" s="11"/>
+      <c r="C198" s="10"/>
       <c r="D198" s="7"/>
       <c r="E198" s="7"/>
       <c r="F198" s="7"/>
@@ -15077,7 +15071,7 @@
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="7"/>
       <c r="B199" s="7"/>
-      <c r="C199" s="11"/>
+      <c r="C199" s="10"/>
       <c r="D199" s="7"/>
       <c r="E199" s="7"/>
       <c r="F199" s="7"/>
@@ -15104,7 +15098,7 @@
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="7"/>
       <c r="B200" s="7"/>
-      <c r="C200" s="11"/>
+      <c r="C200" s="10"/>
       <c r="D200" s="7"/>
       <c r="E200" s="7"/>
       <c r="F200" s="7"/>
@@ -15131,7 +15125,7 @@
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="7"/>
       <c r="B201" s="7"/>
-      <c r="C201" s="11"/>
+      <c r="C201" s="10"/>
       <c r="D201" s="7"/>
       <c r="E201" s="7"/>
       <c r="F201" s="7"/>
@@ -15158,7 +15152,7 @@
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="7"/>
       <c r="B202" s="7"/>
-      <c r="C202" s="11"/>
+      <c r="C202" s="10"/>
       <c r="D202" s="7"/>
       <c r="E202" s="7"/>
       <c r="F202" s="7"/>
@@ -15185,7 +15179,7 @@
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="7"/>
       <c r="B203" s="7"/>
-      <c r="C203" s="11"/>
+      <c r="C203" s="10"/>
       <c r="D203" s="7"/>
       <c r="E203" s="7"/>
       <c r="F203" s="7"/>
@@ -15212,7 +15206,7 @@
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="7"/>
       <c r="B204" s="7"/>
-      <c r="C204" s="11"/>
+      <c r="C204" s="10"/>
       <c r="D204" s="7"/>
       <c r="E204" s="7"/>
       <c r="F204" s="7"/>
@@ -15239,7 +15233,7 @@
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="7"/>
       <c r="B205" s="7"/>
-      <c r="C205" s="11"/>
+      <c r="C205" s="10"/>
       <c r="D205" s="7"/>
       <c r="E205" s="7"/>
       <c r="F205" s="7"/>
@@ -15266,7 +15260,7 @@
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="7"/>
       <c r="B206" s="7"/>
-      <c r="C206" s="11"/>
+      <c r="C206" s="10"/>
       <c r="D206" s="7"/>
       <c r="E206" s="7"/>
       <c r="F206" s="7"/>
@@ -15293,7 +15287,7 @@
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="7"/>
       <c r="B207" s="7"/>
-      <c r="C207" s="11"/>
+      <c r="C207" s="10"/>
       <c r="D207" s="7"/>
       <c r="E207" s="7"/>
       <c r="F207" s="7"/>
@@ -15320,7 +15314,7 @@
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="7"/>
       <c r="B208" s="7"/>
-      <c r="C208" s="11"/>
+      <c r="C208" s="10"/>
       <c r="D208" s="7"/>
       <c r="E208" s="7"/>
       <c r="F208" s="7"/>
@@ -15347,7 +15341,7 @@
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="7"/>
       <c r="B209" s="7"/>
-      <c r="C209" s="11"/>
+      <c r="C209" s="10"/>
       <c r="D209" s="7"/>
       <c r="E209" s="7"/>
       <c r="F209" s="7"/>
@@ -15374,7 +15368,7 @@
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="7"/>
       <c r="B210" s="7"/>
-      <c r="C210" s="11"/>
+      <c r="C210" s="10"/>
       <c r="D210" s="7"/>
       <c r="E210" s="7"/>
       <c r="F210" s="7"/>
@@ -15401,7 +15395,7 @@
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="7"/>
       <c r="B211" s="7"/>
-      <c r="C211" s="11"/>
+      <c r="C211" s="10"/>
       <c r="D211" s="7"/>
       <c r="E211" s="7"/>
       <c r="F211" s="7"/>
@@ -15428,7 +15422,7 @@
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="7"/>
       <c r="B212" s="7"/>
-      <c r="C212" s="11"/>
+      <c r="C212" s="10"/>
       <c r="D212" s="7"/>
       <c r="E212" s="7"/>
       <c r="F212" s="7"/>
@@ -15455,7 +15449,7 @@
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="7"/>
       <c r="B213" s="7"/>
-      <c r="C213" s="11"/>
+      <c r="C213" s="10"/>
       <c r="D213" s="7"/>
       <c r="E213" s="7"/>
       <c r="F213" s="7"/>
@@ -15482,7 +15476,7 @@
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="7"/>
       <c r="B214" s="7"/>
-      <c r="C214" s="11"/>
+      <c r="C214" s="10"/>
       <c r="D214" s="7"/>
       <c r="E214" s="7"/>
       <c r="F214" s="7"/>
@@ -15509,7 +15503,7 @@
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="7"/>
       <c r="B215" s="7"/>
-      <c r="C215" s="11"/>
+      <c r="C215" s="10"/>
       <c r="D215" s="7"/>
       <c r="E215" s="7"/>
       <c r="F215" s="7"/>
@@ -15536,7 +15530,7 @@
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="7"/>
       <c r="B216" s="7"/>
-      <c r="C216" s="11"/>
+      <c r="C216" s="10"/>
       <c r="D216" s="7"/>
       <c r="E216" s="7"/>
       <c r="F216" s="7"/>
@@ -15563,7 +15557,7 @@
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="7"/>
       <c r="B217" s="7"/>
-      <c r="C217" s="11"/>
+      <c r="C217" s="10"/>
       <c r="D217" s="7"/>
       <c r="E217" s="7"/>
       <c r="F217" s="7"/>
@@ -15590,7 +15584,7 @@
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="7"/>
       <c r="B218" s="7"/>
-      <c r="C218" s="11"/>
+      <c r="C218" s="10"/>
       <c r="D218" s="7"/>
       <c r="E218" s="7"/>
       <c r="F218" s="7"/>
@@ -15617,7 +15611,7 @@
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="7"/>
       <c r="B219" s="7"/>
-      <c r="C219" s="11"/>
+      <c r="C219" s="10"/>
       <c r="D219" s="7"/>
       <c r="E219" s="7"/>
       <c r="F219" s="7"/>
@@ -15644,7 +15638,7 @@
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="7"/>
       <c r="B220" s="7"/>
-      <c r="C220" s="11"/>
+      <c r="C220" s="10"/>
       <c r="D220" s="7"/>
       <c r="E220" s="7"/>
       <c r="F220" s="7"/>
@@ -15671,7 +15665,7 @@
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="7"/>
       <c r="B221" s="7"/>
-      <c r="C221" s="11"/>
+      <c r="C221" s="10"/>
       <c r="D221" s="7"/>
       <c r="E221" s="7"/>
       <c r="F221" s="7"/>
@@ -15698,7 +15692,7 @@
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="7"/>
       <c r="B222" s="7"/>
-      <c r="C222" s="11"/>
+      <c r="C222" s="10"/>
       <c r="D222" s="7"/>
       <c r="E222" s="7"/>
       <c r="F222" s="7"/>
@@ -15725,7 +15719,7 @@
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="7"/>
       <c r="B223" s="7"/>
-      <c r="C223" s="11"/>
+      <c r="C223" s="10"/>
       <c r="D223" s="7"/>
       <c r="E223" s="7"/>
       <c r="F223" s="7"/>
@@ -15752,7 +15746,7 @@
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="7"/>
       <c r="B224" s="7"/>
-      <c r="C224" s="11"/>
+      <c r="C224" s="10"/>
       <c r="D224" s="7"/>
       <c r="E224" s="7"/>
       <c r="F224" s="7"/>
@@ -15779,7 +15773,7 @@
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="7"/>
       <c r="B225" s="7"/>
-      <c r="C225" s="11"/>
+      <c r="C225" s="10"/>
       <c r="D225" s="7"/>
       <c r="E225" s="7"/>
       <c r="F225" s="7"/>
@@ -15806,7 +15800,7 @@
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="7"/>
       <c r="B226" s="7"/>
-      <c r="C226" s="11"/>
+      <c r="C226" s="10"/>
       <c r="D226" s="7"/>
       <c r="E226" s="7"/>
       <c r="F226" s="7"/>
@@ -15833,7 +15827,7 @@
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="7"/>
       <c r="B227" s="7"/>
-      <c r="C227" s="11"/>
+      <c r="C227" s="10"/>
       <c r="D227" s="7"/>
       <c r="E227" s="7"/>
       <c r="F227" s="7"/>
@@ -15860,7 +15854,7 @@
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="7"/>
       <c r="B228" s="7"/>
-      <c r="C228" s="11"/>
+      <c r="C228" s="10"/>
       <c r="D228" s="7"/>
       <c r="E228" s="7"/>
       <c r="F228" s="7"/>
@@ -15887,7 +15881,7 @@
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="7"/>
       <c r="B229" s="7"/>
-      <c r="C229" s="11"/>
+      <c r="C229" s="10"/>
       <c r="D229" s="7"/>
       <c r="E229" s="7"/>
       <c r="F229" s="7"/>
@@ -15914,7 +15908,7 @@
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="7"/>
       <c r="B230" s="7"/>
-      <c r="C230" s="11"/>
+      <c r="C230" s="10"/>
       <c r="D230" s="7"/>
       <c r="E230" s="7"/>
       <c r="F230" s="7"/>
@@ -15941,7 +15935,7 @@
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="7"/>
       <c r="B231" s="7"/>
-      <c r="C231" s="11"/>
+      <c r="C231" s="10"/>
       <c r="D231" s="7"/>
       <c r="E231" s="7"/>
       <c r="F231" s="7"/>
@@ -15968,7 +15962,7 @@
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="7"/>
       <c r="B232" s="7"/>
-      <c r="C232" s="11"/>
+      <c r="C232" s="10"/>
       <c r="D232" s="7"/>
       <c r="E232" s="7"/>
       <c r="F232" s="7"/>
@@ -15995,7 +15989,7 @@
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="7"/>
       <c r="B233" s="7"/>
-      <c r="C233" s="11"/>
+      <c r="C233" s="10"/>
       <c r="D233" s="7"/>
       <c r="E233" s="7"/>
       <c r="F233" s="7"/>
@@ -16022,7 +16016,7 @@
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="7"/>
       <c r="B234" s="7"/>
-      <c r="C234" s="11"/>
+      <c r="C234" s="10"/>
       <c r="D234" s="7"/>
       <c r="E234" s="7"/>
       <c r="F234" s="7"/>
@@ -16049,7 +16043,7 @@
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="7"/>
       <c r="B235" s="7"/>
-      <c r="C235" s="11"/>
+      <c r="C235" s="10"/>
       <c r="D235" s="7"/>
       <c r="E235" s="7"/>
       <c r="F235" s="7"/>
@@ -16076,7 +16070,7 @@
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="7"/>
       <c r="B236" s="7"/>
-      <c r="C236" s="11"/>
+      <c r="C236" s="10"/>
       <c r="D236" s="7"/>
       <c r="E236" s="7"/>
       <c r="F236" s="7"/>
@@ -16103,7 +16097,7 @@
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="7"/>
       <c r="B237" s="7"/>
-      <c r="C237" s="11"/>
+      <c r="C237" s="10"/>
       <c r="D237" s="7"/>
       <c r="E237" s="7"/>
       <c r="F237" s="7"/>
@@ -16130,7 +16124,7 @@
     <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="7"/>
       <c r="B238" s="7"/>
-      <c r="C238" s="11"/>
+      <c r="C238" s="10"/>
       <c r="D238" s="7"/>
       <c r="E238" s="7"/>
       <c r="F238" s="7"/>
@@ -16157,7 +16151,7 @@
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="7"/>
       <c r="B239" s="7"/>
-      <c r="C239" s="11"/>
+      <c r="C239" s="10"/>
       <c r="D239" s="7"/>
       <c r="E239" s="7"/>
       <c r="F239" s="7"/>
@@ -16184,7 +16178,7 @@
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="7"/>
       <c r="B240" s="7"/>
-      <c r="C240" s="11"/>
+      <c r="C240" s="10"/>
       <c r="D240" s="7"/>
       <c r="E240" s="7"/>
       <c r="F240" s="7"/>
@@ -16211,7 +16205,7 @@
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="7"/>
       <c r="B241" s="7"/>
-      <c r="C241" s="11"/>
+      <c r="C241" s="10"/>
       <c r="D241" s="7"/>
       <c r="E241" s="7"/>
       <c r="F241" s="7"/>
@@ -16238,7 +16232,7 @@
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="7"/>
       <c r="B242" s="7"/>
-      <c r="C242" s="11"/>
+      <c r="C242" s="10"/>
       <c r="D242" s="7"/>
       <c r="E242" s="7"/>
       <c r="F242" s="7"/>
@@ -16265,7 +16259,7 @@
     <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="7"/>
       <c r="B243" s="7"/>
-      <c r="C243" s="11"/>
+      <c r="C243" s="10"/>
       <c r="D243" s="7"/>
       <c r="E243" s="7"/>
       <c r="F243" s="7"/>
@@ -16292,7 +16286,7 @@
     <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="7"/>
       <c r="B244" s="7"/>
-      <c r="C244" s="11"/>
+      <c r="C244" s="10"/>
       <c r="D244" s="7"/>
       <c r="E244" s="7"/>
       <c r="F244" s="7"/>
@@ -16319,7 +16313,7 @@
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="7"/>
       <c r="B245" s="7"/>
-      <c r="C245" s="11"/>
+      <c r="C245" s="10"/>
       <c r="D245" s="7"/>
       <c r="E245" s="7"/>
       <c r="F245" s="7"/>
@@ -16346,7 +16340,7 @@
     <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="7"/>
       <c r="B246" s="7"/>
-      <c r="C246" s="11"/>
+      <c r="C246" s="10"/>
       <c r="D246" s="7"/>
       <c r="E246" s="7"/>
       <c r="F246" s="7"/>
@@ -16373,7 +16367,7 @@
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="7"/>
       <c r="B247" s="7"/>
-      <c r="C247" s="11"/>
+      <c r="C247" s="10"/>
       <c r="D247" s="7"/>
       <c r="E247" s="7"/>
       <c r="F247" s="7"/>
@@ -16400,7 +16394,7 @@
     <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="7"/>
       <c r="B248" s="7"/>
-      <c r="C248" s="11"/>
+      <c r="C248" s="10"/>
       <c r="D248" s="7"/>
       <c r="E248" s="7"/>
       <c r="F248" s="7"/>
@@ -16427,7 +16421,7 @@
     <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="7"/>
       <c r="B249" s="7"/>
-      <c r="C249" s="11"/>
+      <c r="C249" s="10"/>
       <c r="D249" s="7"/>
       <c r="E249" s="7"/>
       <c r="F249" s="7"/>
@@ -16454,7 +16448,7 @@
     <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="7"/>
       <c r="B250" s="7"/>
-      <c r="C250" s="11"/>
+      <c r="C250" s="10"/>
       <c r="D250" s="7"/>
       <c r="E250" s="7"/>
       <c r="F250" s="7"/>
@@ -16481,7 +16475,7 @@
     <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="7"/>
       <c r="B251" s="7"/>
-      <c r="C251" s="11"/>
+      <c r="C251" s="10"/>
       <c r="D251" s="7"/>
       <c r="E251" s="7"/>
       <c r="F251" s="7"/>
@@ -16508,7 +16502,7 @@
     <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="7"/>
       <c r="B252" s="7"/>
-      <c r="C252" s="11"/>
+      <c r="C252" s="10"/>
       <c r="D252" s="7"/>
       <c r="E252" s="7"/>
       <c r="F252" s="7"/>
@@ -16535,7 +16529,7 @@
     <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="7"/>
       <c r="B253" s="7"/>
-      <c r="C253" s="11"/>
+      <c r="C253" s="10"/>
       <c r="D253" s="7"/>
       <c r="E253" s="7"/>
       <c r="F253" s="7"/>
@@ -16562,7 +16556,7 @@
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="7"/>
       <c r="B254" s="7"/>
-      <c r="C254" s="11"/>
+      <c r="C254" s="10"/>
       <c r="D254" s="7"/>
       <c r="E254" s="7"/>
       <c r="F254" s="7"/>
@@ -16589,7 +16583,7 @@
     <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="7"/>
       <c r="B255" s="7"/>
-      <c r="C255" s="11"/>
+      <c r="C255" s="10"/>
       <c r="D255" s="7"/>
       <c r="E255" s="7"/>
       <c r="F255" s="7"/>
@@ -16616,7 +16610,7 @@
     <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="7"/>
       <c r="B256" s="7"/>
-      <c r="C256" s="11"/>
+      <c r="C256" s="10"/>
       <c r="D256" s="7"/>
       <c r="E256" s="7"/>
       <c r="F256" s="7"/>
@@ -16643,7 +16637,7 @@
     <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="7"/>
       <c r="B257" s="7"/>
-      <c r="C257" s="11"/>
+      <c r="C257" s="10"/>
       <c r="D257" s="7"/>
       <c r="E257" s="7"/>
       <c r="F257" s="7"/>
@@ -16670,7 +16664,7 @@
     <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="7"/>
       <c r="B258" s="7"/>
-      <c r="C258" s="11"/>
+      <c r="C258" s="10"/>
       <c r="D258" s="7"/>
       <c r="E258" s="7"/>
       <c r="F258" s="7"/>
@@ -16697,7 +16691,7 @@
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="7"/>
       <c r="B259" s="7"/>
-      <c r="C259" s="11"/>
+      <c r="C259" s="10"/>
       <c r="D259" s="7"/>
       <c r="E259" s="7"/>
       <c r="F259" s="7"/>
@@ -16724,7 +16718,7 @@
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="7"/>
       <c r="B260" s="7"/>
-      <c r="C260" s="11"/>
+      <c r="C260" s="10"/>
       <c r="D260" s="7"/>
       <c r="E260" s="7"/>
       <c r="F260" s="7"/>
@@ -16751,7 +16745,7 @@
     <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="7"/>
       <c r="B261" s="7"/>
-      <c r="C261" s="11"/>
+      <c r="C261" s="10"/>
       <c r="D261" s="7"/>
       <c r="E261" s="7"/>
       <c r="F261" s="7"/>
@@ -16778,7 +16772,7 @@
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="7"/>
       <c r="B262" s="7"/>
-      <c r="C262" s="11"/>
+      <c r="C262" s="10"/>
       <c r="D262" s="7"/>
       <c r="E262" s="7"/>
       <c r="F262" s="7"/>
@@ -16805,7 +16799,7 @@
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="7"/>
       <c r="B263" s="7"/>
-      <c r="C263" s="11"/>
+      <c r="C263" s="10"/>
       <c r="D263" s="7"/>
       <c r="E263" s="7"/>
       <c r="F263" s="7"/>
@@ -16832,7 +16826,7 @@
     <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="7"/>
       <c r="B264" s="7"/>
-      <c r="C264" s="11"/>
+      <c r="C264" s="10"/>
       <c r="D264" s="7"/>
       <c r="E264" s="7"/>
       <c r="F264" s="7"/>
@@ -16859,7 +16853,7 @@
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="7"/>
       <c r="B265" s="7"/>
-      <c r="C265" s="11"/>
+      <c r="C265" s="10"/>
       <c r="D265" s="7"/>
       <c r="E265" s="7"/>
       <c r="F265" s="7"/>
@@ -16886,7 +16880,7 @@
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="7"/>
       <c r="B266" s="7"/>
-      <c r="C266" s="11"/>
+      <c r="C266" s="10"/>
       <c r="D266" s="7"/>
       <c r="E266" s="7"/>
       <c r="F266" s="7"/>
@@ -16913,7 +16907,7 @@
     <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="7"/>
       <c r="B267" s="7"/>
-      <c r="C267" s="11"/>
+      <c r="C267" s="10"/>
       <c r="D267" s="7"/>
       <c r="E267" s="7"/>
       <c r="F267" s="7"/>
@@ -16940,7 +16934,7 @@
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="7"/>
       <c r="B268" s="7"/>
-      <c r="C268" s="11"/>
+      <c r="C268" s="10"/>
       <c r="D268" s="7"/>
       <c r="E268" s="7"/>
       <c r="F268" s="7"/>
@@ -16967,7 +16961,7 @@
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="7"/>
       <c r="B269" s="7"/>
-      <c r="C269" s="11"/>
+      <c r="C269" s="10"/>
       <c r="D269" s="7"/>
       <c r="E269" s="7"/>
       <c r="F269" s="7"/>
@@ -16994,7 +16988,7 @@
     <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="7"/>
       <c r="B270" s="7"/>
-      <c r="C270" s="11"/>
+      <c r="C270" s="10"/>
       <c r="D270" s="7"/>
       <c r="E270" s="7"/>
       <c r="F270" s="7"/>
@@ -17021,7 +17015,7 @@
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="7"/>
       <c r="B271" s="7"/>
-      <c r="C271" s="11"/>
+      <c r="C271" s="10"/>
       <c r="D271" s="7"/>
       <c r="E271" s="7"/>
       <c r="F271" s="7"/>
@@ -17048,7 +17042,7 @@
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="7"/>
       <c r="B272" s="7"/>
-      <c r="C272" s="11"/>
+      <c r="C272" s="10"/>
       <c r="D272" s="7"/>
       <c r="E272" s="7"/>
       <c r="F272" s="7"/>
@@ -17075,7 +17069,7 @@
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="7"/>
       <c r="B273" s="7"/>
-      <c r="C273" s="11"/>
+      <c r="C273" s="10"/>
       <c r="D273" s="7"/>
       <c r="E273" s="7"/>
       <c r="F273" s="7"/>
@@ -17102,7 +17096,7 @@
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="7"/>
       <c r="B274" s="7"/>
-      <c r="C274" s="11"/>
+      <c r="C274" s="10"/>
       <c r="D274" s="7"/>
       <c r="E274" s="7"/>
       <c r="F274" s="7"/>
@@ -17129,7 +17123,7 @@
     <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="7"/>
       <c r="B275" s="7"/>
-      <c r="C275" s="11"/>
+      <c r="C275" s="10"/>
       <c r="D275" s="7"/>
       <c r="E275" s="7"/>
       <c r="F275" s="7"/>
@@ -17156,7 +17150,7 @@
     <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="7"/>
       <c r="B276" s="7"/>
-      <c r="C276" s="11"/>
+      <c r="C276" s="10"/>
       <c r="D276" s="7"/>
       <c r="E276" s="7"/>
       <c r="F276" s="7"/>
@@ -17183,7 +17177,7 @@
     <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="7"/>
       <c r="B277" s="7"/>
-      <c r="C277" s="11"/>
+      <c r="C277" s="10"/>
       <c r="D277" s="7"/>
       <c r="E277" s="7"/>
       <c r="F277" s="7"/>
@@ -17210,7 +17204,7 @@
     <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="7"/>
       <c r="B278" s="7"/>
-      <c r="C278" s="11"/>
+      <c r="C278" s="10"/>
       <c r="D278" s="7"/>
       <c r="E278" s="7"/>
       <c r="F278" s="7"/>
@@ -17237,7 +17231,7 @@
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="7"/>
       <c r="B279" s="7"/>
-      <c r="C279" s="11"/>
+      <c r="C279" s="10"/>
       <c r="D279" s="7"/>
       <c r="E279" s="7"/>
       <c r="F279" s="7"/>
@@ -17264,7 +17258,7 @@
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="7"/>
       <c r="B280" s="7"/>
-      <c r="C280" s="11"/>
+      <c r="C280" s="10"/>
       <c r="D280" s="7"/>
       <c r="E280" s="7"/>
       <c r="F280" s="7"/>
@@ -17291,7 +17285,7 @@
     <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="7"/>
       <c r="B281" s="7"/>
-      <c r="C281" s="11"/>
+      <c r="C281" s="10"/>
       <c r="D281" s="7"/>
       <c r="E281" s="7"/>
       <c r="F281" s="7"/>
@@ -17318,7 +17312,7 @@
     <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="7"/>
       <c r="B282" s="7"/>
-      <c r="C282" s="11"/>
+      <c r="C282" s="10"/>
       <c r="D282" s="7"/>
       <c r="E282" s="7"/>
       <c r="F282" s="7"/>
@@ -17345,7 +17339,7 @@
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="7"/>
       <c r="B283" s="7"/>
-      <c r="C283" s="11"/>
+      <c r="C283" s="10"/>
       <c r="D283" s="7"/>
       <c r="E283" s="7"/>
       <c r="F283" s="7"/>
@@ -17372,7 +17366,7 @@
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="7"/>
       <c r="B284" s="7"/>
-      <c r="C284" s="11"/>
+      <c r="C284" s="10"/>
       <c r="D284" s="7"/>
       <c r="E284" s="7"/>
       <c r="F284" s="7"/>
@@ -17399,7 +17393,7 @@
     <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="7"/>
       <c r="B285" s="7"/>
-      <c r="C285" s="11"/>
+      <c r="C285" s="10"/>
       <c r="D285" s="7"/>
       <c r="E285" s="7"/>
       <c r="F285" s="7"/>
@@ -17426,7 +17420,7 @@
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="7"/>
       <c r="B286" s="7"/>
-      <c r="C286" s="11"/>
+      <c r="C286" s="10"/>
       <c r="D286" s="7"/>
       <c r="E286" s="7"/>
       <c r="F286" s="7"/>
@@ -17453,7 +17447,7 @@
     <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="7"/>
       <c r="B287" s="7"/>
-      <c r="C287" s="11"/>
+      <c r="C287" s="10"/>
       <c r="D287" s="7"/>
       <c r="E287" s="7"/>
       <c r="F287" s="7"/>
@@ -17480,7 +17474,7 @@
     <row r="288" ht="15.75" customHeight="1">
       <c r="A288" s="7"/>
       <c r="B288" s="7"/>
-      <c r="C288" s="11"/>
+      <c r="C288" s="10"/>
       <c r="D288" s="7"/>
       <c r="E288" s="7"/>
       <c r="F288" s="7"/>
@@ -17507,7 +17501,7 @@
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="7"/>
       <c r="B289" s="7"/>
-      <c r="C289" s="11"/>
+      <c r="C289" s="10"/>
       <c r="D289" s="7"/>
       <c r="E289" s="7"/>
       <c r="F289" s="7"/>
@@ -17534,7 +17528,7 @@
     <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="7"/>
       <c r="B290" s="7"/>
-      <c r="C290" s="11"/>
+      <c r="C290" s="10"/>
       <c r="D290" s="7"/>
       <c r="E290" s="7"/>
       <c r="F290" s="7"/>
@@ -17561,7 +17555,7 @@
     <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="7"/>
       <c r="B291" s="7"/>
-      <c r="C291" s="11"/>
+      <c r="C291" s="10"/>
       <c r="D291" s="7"/>
       <c r="E291" s="7"/>
       <c r="F291" s="7"/>
@@ -17588,7 +17582,7 @@
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="7"/>
       <c r="B292" s="7"/>
-      <c r="C292" s="11"/>
+      <c r="C292" s="10"/>
       <c r="D292" s="7"/>
       <c r="E292" s="7"/>
       <c r="F292" s="7"/>
@@ -17615,7 +17609,7 @@
     <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="7"/>
       <c r="B293" s="7"/>
-      <c r="C293" s="11"/>
+      <c r="C293" s="10"/>
       <c r="D293" s="7"/>
       <c r="E293" s="7"/>
       <c r="F293" s="7"/>
@@ -17642,7 +17636,7 @@
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="7"/>
       <c r="B294" s="7"/>
-      <c r="C294" s="11"/>
+      <c r="C294" s="10"/>
       <c r="D294" s="7"/>
       <c r="E294" s="7"/>
       <c r="F294" s="7"/>
@@ -17669,7 +17663,7 @@
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="7"/>
       <c r="B295" s="7"/>
-      <c r="C295" s="11"/>
+      <c r="C295" s="10"/>
       <c r="D295" s="7"/>
       <c r="E295" s="7"/>
       <c r="F295" s="7"/>
@@ -17696,7 +17690,7 @@
     <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="7"/>
       <c r="B296" s="7"/>
-      <c r="C296" s="11"/>
+      <c r="C296" s="10"/>
       <c r="D296" s="7"/>
       <c r="E296" s="7"/>
       <c r="F296" s="7"/>
@@ -17723,7 +17717,7 @@
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="7"/>
       <c r="B297" s="7"/>
-      <c r="C297" s="11"/>
+      <c r="C297" s="10"/>
       <c r="D297" s="7"/>
       <c r="E297" s="7"/>
       <c r="F297" s="7"/>
@@ -17750,7 +17744,7 @@
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="7"/>
       <c r="B298" s="7"/>
-      <c r="C298" s="11"/>
+      <c r="C298" s="10"/>
       <c r="D298" s="7"/>
       <c r="E298" s="7"/>
       <c r="F298" s="7"/>
@@ -17777,7 +17771,7 @@
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="7"/>
       <c r="B299" s="7"/>
-      <c r="C299" s="11"/>
+      <c r="C299" s="10"/>
       <c r="D299" s="7"/>
       <c r="E299" s="7"/>
       <c r="F299" s="7"/>
@@ -17804,7 +17798,7 @@
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="7"/>
       <c r="B300" s="7"/>
-      <c r="C300" s="11"/>
+      <c r="C300" s="10"/>
       <c r="D300" s="7"/>
       <c r="E300" s="7"/>
       <c r="F300" s="7"/>
@@ -17831,7 +17825,7 @@
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="7"/>
       <c r="B301" s="7"/>
-      <c r="C301" s="11"/>
+      <c r="C301" s="10"/>
       <c r="D301" s="7"/>
       <c r="E301" s="7"/>
       <c r="F301" s="7"/>
@@ -17858,7 +17852,7 @@
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="7"/>
       <c r="B302" s="7"/>
-      <c r="C302" s="11"/>
+      <c r="C302" s="10"/>
       <c r="D302" s="7"/>
       <c r="E302" s="7"/>
       <c r="F302" s="7"/>
@@ -17885,7 +17879,7 @@
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="7"/>
       <c r="B303" s="7"/>
-      <c r="C303" s="11"/>
+      <c r="C303" s="10"/>
       <c r="D303" s="7"/>
       <c r="E303" s="7"/>
       <c r="F303" s="7"/>
@@ -17912,7 +17906,7 @@
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="7"/>
       <c r="B304" s="7"/>
-      <c r="C304" s="11"/>
+      <c r="C304" s="10"/>
       <c r="D304" s="7"/>
       <c r="E304" s="7"/>
       <c r="F304" s="7"/>
@@ -17939,7 +17933,7 @@
     <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="7"/>
       <c r="B305" s="7"/>
-      <c r="C305" s="11"/>
+      <c r="C305" s="10"/>
       <c r="D305" s="7"/>
       <c r="E305" s="7"/>
       <c r="F305" s="7"/>
@@ -17966,7 +17960,7 @@
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="7"/>
       <c r="B306" s="7"/>
-      <c r="C306" s="11"/>
+      <c r="C306" s="10"/>
       <c r="D306" s="7"/>
       <c r="E306" s="7"/>
       <c r="F306" s="7"/>
@@ -17993,7 +17987,7 @@
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="7"/>
       <c r="B307" s="7"/>
-      <c r="C307" s="11"/>
+      <c r="C307" s="10"/>
       <c r="D307" s="7"/>
       <c r="E307" s="7"/>
       <c r="F307" s="7"/>
@@ -18020,7 +18014,7 @@
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="7"/>
       <c r="B308" s="7"/>
-      <c r="C308" s="11"/>
+      <c r="C308" s="10"/>
       <c r="D308" s="7"/>
       <c r="E308" s="7"/>
       <c r="F308" s="7"/>
@@ -18047,7 +18041,7 @@
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="7"/>
       <c r="B309" s="7"/>
-      <c r="C309" s="11"/>
+      <c r="C309" s="10"/>
       <c r="D309" s="7"/>
       <c r="E309" s="7"/>
       <c r="F309" s="7"/>
@@ -18074,7 +18068,7 @@
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="7"/>
       <c r="B310" s="7"/>
-      <c r="C310" s="11"/>
+      <c r="C310" s="10"/>
       <c r="D310" s="7"/>
       <c r="E310" s="7"/>
       <c r="F310" s="7"/>
@@ -18101,7 +18095,7 @@
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="7"/>
       <c r="B311" s="7"/>
-      <c r="C311" s="11"/>
+      <c r="C311" s="10"/>
       <c r="D311" s="7"/>
       <c r="E311" s="7"/>
       <c r="F311" s="7"/>
@@ -18128,7 +18122,7 @@
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="7"/>
       <c r="B312" s="7"/>
-      <c r="C312" s="11"/>
+      <c r="C312" s="10"/>
       <c r="D312" s="7"/>
       <c r="E312" s="7"/>
       <c r="F312" s="7"/>
@@ -18155,7 +18149,7 @@
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="7"/>
       <c r="B313" s="7"/>
-      <c r="C313" s="11"/>
+      <c r="C313" s="10"/>
       <c r="D313" s="7"/>
       <c r="E313" s="7"/>
       <c r="F313" s="7"/>
@@ -18182,7 +18176,7 @@
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="7"/>
       <c r="B314" s="7"/>
-      <c r="C314" s="11"/>
+      <c r="C314" s="10"/>
       <c r="D314" s="7"/>
       <c r="E314" s="7"/>
       <c r="F314" s="7"/>
@@ -18209,7 +18203,7 @@
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="7"/>
       <c r="B315" s="7"/>
-      <c r="C315" s="11"/>
+      <c r="C315" s="10"/>
       <c r="D315" s="7"/>
       <c r="E315" s="7"/>
       <c r="F315" s="7"/>
@@ -18236,7 +18230,7 @@
     <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="7"/>
       <c r="B316" s="7"/>
-      <c r="C316" s="11"/>
+      <c r="C316" s="10"/>
       <c r="D316" s="7"/>
       <c r="E316" s="7"/>
       <c r="F316" s="7"/>
@@ -18263,7 +18257,7 @@
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="7"/>
       <c r="B317" s="7"/>
-      <c r="C317" s="11"/>
+      <c r="C317" s="10"/>
       <c r="D317" s="7"/>
       <c r="E317" s="7"/>
       <c r="F317" s="7"/>
@@ -18290,7 +18284,7 @@
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="7"/>
       <c r="B318" s="7"/>
-      <c r="C318" s="11"/>
+      <c r="C318" s="10"/>
       <c r="D318" s="7"/>
       <c r="E318" s="7"/>
       <c r="F318" s="7"/>
@@ -18317,7 +18311,7 @@
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="7"/>
       <c r="B319" s="7"/>
-      <c r="C319" s="11"/>
+      <c r="C319" s="10"/>
       <c r="D319" s="7"/>
       <c r="E319" s="7"/>
       <c r="F319" s="7"/>
@@ -18344,7 +18338,7 @@
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="7"/>
       <c r="B320" s="7"/>
-      <c r="C320" s="11"/>
+      <c r="C320" s="10"/>
       <c r="D320" s="7"/>
       <c r="E320" s="7"/>
       <c r="F320" s="7"/>
@@ -18371,7 +18365,7 @@
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="7"/>
       <c r="B321" s="7"/>
-      <c r="C321" s="11"/>
+      <c r="C321" s="10"/>
       <c r="D321" s="7"/>
       <c r="E321" s="7"/>
       <c r="F321" s="7"/>
@@ -18398,7 +18392,7 @@
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="7"/>
       <c r="B322" s="7"/>
-      <c r="C322" s="11"/>
+      <c r="C322" s="10"/>
       <c r="D322" s="7"/>
       <c r="E322" s="7"/>
       <c r="F322" s="7"/>
@@ -18425,7 +18419,7 @@
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="7"/>
       <c r="B323" s="7"/>
-      <c r="C323" s="11"/>
+      <c r="C323" s="10"/>
       <c r="D323" s="7"/>
       <c r="E323" s="7"/>
       <c r="F323" s="7"/>
@@ -18452,7 +18446,7 @@
     <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="7"/>
       <c r="B324" s="7"/>
-      <c r="C324" s="11"/>
+      <c r="C324" s="10"/>
       <c r="D324" s="7"/>
       <c r="E324" s="7"/>
       <c r="F324" s="7"/>
@@ -18479,7 +18473,7 @@
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="7"/>
       <c r="B325" s="7"/>
-      <c r="C325" s="11"/>
+      <c r="C325" s="10"/>
       <c r="D325" s="7"/>
       <c r="E325" s="7"/>
       <c r="F325" s="7"/>
@@ -18506,7 +18500,7 @@
     <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="7"/>
       <c r="B326" s="7"/>
-      <c r="C326" s="11"/>
+      <c r="C326" s="10"/>
       <c r="D326" s="7"/>
       <c r="E326" s="7"/>
       <c r="F326" s="7"/>
@@ -18533,7 +18527,7 @@
     <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="7"/>
       <c r="B327" s="7"/>
-      <c r="C327" s="11"/>
+      <c r="C327" s="10"/>
       <c r="D327" s="7"/>
       <c r="E327" s="7"/>
       <c r="F327" s="7"/>
@@ -18560,7 +18554,7 @@
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="7"/>
       <c r="B328" s="7"/>
-      <c r="C328" s="11"/>
+      <c r="C328" s="10"/>
       <c r="D328" s="7"/>
       <c r="E328" s="7"/>
       <c r="F328" s="7"/>
@@ -18587,7 +18581,7 @@
     <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="7"/>
       <c r="B329" s="7"/>
-      <c r="C329" s="11"/>
+      <c r="C329" s="10"/>
       <c r="D329" s="7"/>
       <c r="E329" s="7"/>
       <c r="F329" s="7"/>
@@ -18614,7 +18608,7 @@
     <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="7"/>
       <c r="B330" s="7"/>
-      <c r="C330" s="11"/>
+      <c r="C330" s="10"/>
       <c r="D330" s="7"/>
       <c r="E330" s="7"/>
       <c r="F330" s="7"/>
@@ -18641,7 +18635,7 @@
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="7"/>
       <c r="B331" s="7"/>
-      <c r="C331" s="11"/>
+      <c r="C331" s="10"/>
       <c r="D331" s="7"/>
       <c r="E331" s="7"/>
       <c r="F331" s="7"/>
@@ -18668,7 +18662,7 @@
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="7"/>
       <c r="B332" s="7"/>
-      <c r="C332" s="11"/>
+      <c r="C332" s="10"/>
       <c r="D332" s="7"/>
       <c r="E332" s="7"/>
       <c r="F332" s="7"/>
@@ -18695,7 +18689,7 @@
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="7"/>
       <c r="B333" s="7"/>
-      <c r="C333" s="11"/>
+      <c r="C333" s="10"/>
       <c r="D333" s="7"/>
       <c r="E333" s="7"/>
       <c r="F333" s="7"/>
